--- a/data/data_shichigawahama_w4.xlsx
+++ b/data/data_shichigawahama_w4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6DACEF-1426-449B-A783-F195FC5F5E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45CFA08-47D9-4EE7-86ED-F032BE3B8FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="539">
   <si>
     <t>id</t>
   </si>
@@ -4898,6 +4898,263 @@
   </si>
   <si>
     <t>赤間陽</t>
+  </si>
+  <si>
+    <t>age_w4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>family_number</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>無</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v32_successor_yes_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v32_successor_no_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v32_successor_dontknow_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>岡田</t>
+    <rPh sb="0" eb="2">
+      <t>オカダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東海林昭一</t>
+    <rPh sb="0" eb="3">
+      <t>ショウジ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ショウイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三浦 康市</t>
+    <rPh sb="0" eb="5">
+      <t>ミウラ　ヤスイチ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東宮浜</t>
+    <rPh sb="0" eb="2">
+      <t>トウグウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>我妻　周悦</t>
+    <rPh sb="0" eb="2">
+      <t>ワガツマ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>エツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>花渕浜</t>
+    <rPh sb="0" eb="1">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>フチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木　吉秋</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨシアキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木　吉昭</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨシアキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吉田浜</t>
+    <rPh sb="0" eb="2">
+      <t>ヨシダ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ハマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木君夫</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キミオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐藤　寛也</t>
+    <rPh sb="0" eb="2">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>要害</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウガイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>佐藤　太郎</t>
+    <rPh sb="0" eb="2">
+      <t>サトウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鈴木　君夫</t>
+    <rPh sb="0" eb="2">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キミオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>三嶋重昭</t>
+    <rPh sb="0" eb="2">
+      <t>ミシマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シゲアキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>v33_farmland_intention_myself_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v33_farmland_intention_ja_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v33_farmland_intention_individual_farm_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v34_contractor_address</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v34_contractor_name</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_expansion_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention__maintain_status_quo_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_reduction_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_quit_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_lend_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_sell_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v36_farming_type_corporate_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v36_farming_type_individual_farm_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v37_preferred_farmland_manager_corporate_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v37_preferred_farmland_manager_individual_farm_w4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v38_future_farm_operator_diverse_farm</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v38_future_farm_operator_large_farm</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v38_future_farm_operator_group_farming</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v38_future_farm_operator_corporate_farming</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v38_future_farm_operator_ja_corporate_farming</t>
+    <phoneticPr fontId="5"/>
   </si>
 </sst>
 </file>
@@ -4953,12 +5210,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -4973,8 +5236,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -5255,15 +5520,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E242"/>
+  <dimension ref="A1:AD242"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="57.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.08203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="45.25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.9140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.9140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.25" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="28.4140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.58203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="38.08203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="41.5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="44.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>373</v>
       </c>
@@ -5279,8 +5568,83 @@
       <c r="E1" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G1" t="s">
+        <v>499</v>
+      </c>
+      <c r="H1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J1" t="s">
+        <v>503</v>
+      </c>
+      <c r="K1" t="s">
+        <v>519</v>
+      </c>
+      <c r="L1" t="s">
+        <v>520</v>
+      </c>
+      <c r="M1" t="s">
+        <v>521</v>
+      </c>
+      <c r="N1" t="s">
+        <v>522</v>
+      </c>
+      <c r="O1" t="s">
+        <v>523</v>
+      </c>
+      <c r="P1" t="s">
+        <v>524</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>525</v>
+      </c>
+      <c r="R1" t="s">
+        <v>526</v>
+      </c>
+      <c r="S1" t="s">
+        <v>527</v>
+      </c>
+      <c r="T1" t="s">
+        <v>528</v>
+      </c>
+      <c r="U1" t="s">
+        <v>529</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="W1" t="s">
+        <v>531</v>
+      </c>
+      <c r="X1" t="s">
+        <v>532</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>533</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>536</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5296,8 +5660,32 @@
       <c r="E2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>59</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5313,8 +5701,32 @@
       <c r="E3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5330,8 +5742,29 @@
       <c r="E4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>64</v>
+      </c>
+      <c r="G4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5347,8 +5780,26 @@
       <c r="E5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>81</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5364,8 +5815,23 @@
       <c r="E6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>62</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5381,8 +5847,29 @@
       <c r="E7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>77</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5398,8 +5885,23 @@
       <c r="E8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>70</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5415,8 +5917,26 @@
       <c r="E9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>6</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5432,8 +5952,32 @@
       <c r="E10" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>67</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10" t="s">
+        <v>504</v>
+      </c>
+      <c r="O10" t="s">
+        <v>505</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5449,8 +5993,29 @@
       <c r="E11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>76</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5466,8 +6031,23 @@
       <c r="E12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>69</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5483,8 +6063,17 @@
       <c r="E13" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>80</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5500,8 +6089,32 @@
       <c r="E14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" t="s">
+        <v>506</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5518,7 +6131,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:30">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5534,8 +6147,26 @@
       <c r="E16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>83</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5551,8 +6182,23 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5568,8 +6214,29 @@
       <c r="E18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>59</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5586,7 +6253,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:30">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5602,8 +6269,23 @@
       <c r="E20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>71</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5619,8 +6301,29 @@
       <c r="E21" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21">
+        <v>49</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5637,7 +6340,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:30">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5653,8 +6356,26 @@
       <c r="E23" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23">
+        <v>48</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5670,8 +6391,26 @@
       <c r="E24" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24">
+        <v>76</v>
+      </c>
+      <c r="G24">
+        <v>6</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5687,8 +6426,32 @@
       <c r="E25" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25">
+        <v>63</v>
+      </c>
+      <c r="G25">
+        <v>4</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" t="s">
+        <v>506</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5705,7 +6468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:30">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5722,7 +6485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:30">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5738,8 +6501,26 @@
       <c r="E28" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28">
+        <v>51</v>
+      </c>
+      <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Z28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5755,8 +6536,29 @@
       <c r="E29" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29">
+        <v>57</v>
+      </c>
+      <c r="G29">
+        <v>4</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5772,8 +6574,29 @@
       <c r="E30" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30">
+        <v>60</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <v>1</v>
+      </c>
+      <c r="W30">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5789,8 +6612,26 @@
       <c r="E31" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31">
+        <v>77</v>
+      </c>
+      <c r="G31">
+        <v>7</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5806,8 +6647,26 @@
       <c r="E32" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32">
+        <v>72</v>
+      </c>
+      <c r="G32">
+        <v>2</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
+      </c>
+      <c r="AD32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5823,8 +6682,29 @@
       <c r="E33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33">
+        <v>54</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="AD33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5840,8 +6720,29 @@
       <c r="E34" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34">
+        <v>54</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="AC34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5857,8 +6758,29 @@
       <c r="E35" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35">
+        <v>64</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
+      </c>
+      <c r="V35">
+        <v>1</v>
+      </c>
+      <c r="AD35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5874,8 +6796,35 @@
       <c r="E36" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36">
+        <v>60</v>
+      </c>
+      <c r="G36">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="s">
+        <v>507</v>
+      </c>
+      <c r="O36" t="s">
+        <v>508</v>
+      </c>
+      <c r="U36">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>1</v>
+      </c>
+      <c r="AD36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5891,8 +6840,26 @@
       <c r="E37" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37">
+        <v>64</v>
+      </c>
+      <c r="G37">
+        <v>4</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="AD37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5908,8 +6875,26 @@
       <c r="E38" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38">
+        <v>62</v>
+      </c>
+      <c r="G38">
+        <v>5</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="W38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5925,8 +6910,23 @@
       <c r="E39" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39">
+        <v>72</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>1</v>
+      </c>
+      <c r="AD39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5943,7 +6943,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:30">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5959,8 +6959,26 @@
       <c r="E41" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41">
+        <v>53</v>
+      </c>
+      <c r="G41">
+        <v>5</v>
+      </c>
+      <c r="I41">
+        <v>1</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5976,8 +6994,17 @@
       <c r="E42" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42">
+        <v>81</v>
+      </c>
+      <c r="G42">
+        <v>3</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5993,8 +7020,32 @@
       <c r="E43" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43">
+        <v>54</v>
+      </c>
+      <c r="G43">
+        <v>4</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="V43">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>1</v>
+      </c>
+      <c r="AB43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6010,8 +7061,26 @@
       <c r="E44" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44">
+        <v>56</v>
+      </c>
+      <c r="G44">
+        <v>3</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="AD44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6027,8 +7096,26 @@
       <c r="E45" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45">
+        <v>60</v>
+      </c>
+      <c r="G45">
+        <v>3</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="AD45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6044,8 +7131,29 @@
       <c r="E46" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46">
+        <v>75</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+      <c r="I46">
+        <v>1</v>
+      </c>
+      <c r="L46">
+        <v>1</v>
+      </c>
+      <c r="U46">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>1</v>
+      </c>
+      <c r="AD46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6061,8 +7169,29 @@
       <c r="E47" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47">
+        <v>78</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="I47">
+        <v>1</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>1</v>
+      </c>
+      <c r="AB47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6079,7 +7208,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:30">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6095,8 +7224,23 @@
       <c r="E49" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49">
+        <v>49</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6112,8 +7256,23 @@
       <c r="E50" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50">
+        <v>73</v>
+      </c>
+      <c r="G50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="L50">
+        <v>1</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6129,8 +7288,26 @@
       <c r="E51" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51">
+        <v>83</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="AD51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6147,7 +7324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:30">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6164,7 +7341,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:30">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6180,8 +7357,23 @@
       <c r="E54" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54">
+        <v>62</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="L54">
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="AD54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6197,8 +7389,23 @@
       <c r="E55" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s">
+        <v>500</v>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6214,8 +7421,29 @@
       <c r="E56" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56">
+        <v>78</v>
+      </c>
+      <c r="G56">
+        <v>2</v>
+      </c>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>1</v>
+      </c>
+      <c r="X56">
+        <v>1</v>
+      </c>
+      <c r="AD56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6231,8 +7459,29 @@
       <c r="E57" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57">
+        <v>63</v>
+      </c>
+      <c r="G57">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="Q57">
+        <v>1</v>
+      </c>
+      <c r="Y57">
+        <v>1</v>
+      </c>
+      <c r="AA57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6248,8 +7497,29 @@
       <c r="E58" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58">
+        <v>50</v>
+      </c>
+      <c r="G58">
+        <v>8</v>
+      </c>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="V58">
+        <v>1</v>
+      </c>
+      <c r="X58">
+        <v>1</v>
+      </c>
+      <c r="AB58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6265,8 +7535,29 @@
       <c r="E59" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59">
+        <v>77</v>
+      </c>
+      <c r="G59">
+        <v>7</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="L59">
+        <v>1</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="AB59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6282,8 +7573,32 @@
       <c r="E60" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60">
+        <v>72</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+      <c r="V60">
+        <v>1</v>
+      </c>
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="AD60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6300,7 +7615,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:30">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6316,8 +7631,20 @@
       <c r="E62" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62">
+        <v>55</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="AB62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6333,8 +7660,29 @@
       <c r="E63" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63">
+        <v>65</v>
+      </c>
+      <c r="G63">
+        <v>3</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>1</v>
+      </c>
+      <c r="V63">
+        <v>1</v>
+      </c>
+      <c r="X63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6350,8 +7698,20 @@
       <c r="E64" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64">
+        <v>74</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6368,7 +7728,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:30">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6384,8 +7744,29 @@
       <c r="E66" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66">
+        <v>89</v>
+      </c>
+      <c r="G66">
+        <v>7</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+      <c r="N66" t="s">
+        <v>507</v>
+      </c>
+      <c r="O66" t="s">
+        <v>508</v>
+      </c>
+      <c r="S66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6402,7 +7783,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:30">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6418,8 +7799,29 @@
       <c r="E68" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68">
+        <v>70</v>
+      </c>
+      <c r="G68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="AC68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6435,8 +7837,29 @@
       <c r="E69" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="G69">
+        <v>6</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="Q69">
+        <v>1</v>
+      </c>
+      <c r="W69">
+        <v>1</v>
+      </c>
+      <c r="Y69">
+        <v>1</v>
+      </c>
+      <c r="Z69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6452,8 +7875,29 @@
       <c r="E70" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70">
+        <v>64</v>
+      </c>
+      <c r="G70">
+        <v>3</v>
+      </c>
+      <c r="J70">
+        <v>1</v>
+      </c>
+      <c r="L70">
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+      <c r="X70">
+        <v>1</v>
+      </c>
+      <c r="AC70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6469,8 +7913,26 @@
       <c r="E71" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71">
+        <v>76</v>
+      </c>
+      <c r="G71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>1</v>
+      </c>
+      <c r="L71">
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>1</v>
+      </c>
+      <c r="AC71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6486,8 +7948,29 @@
       <c r="E72" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72">
+        <v>54</v>
+      </c>
+      <c r="G72">
+        <v>6</v>
+      </c>
+      <c r="H72">
+        <v>1</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="AD72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6503,8 +7986,26 @@
       <c r="E73" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73">
+        <v>79</v>
+      </c>
+      <c r="G73">
+        <v>7</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>1</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="W73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6521,7 +8022,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:30">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6538,7 +8039,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:30">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6555,7 +8056,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:30">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6571,8 +8072,26 @@
       <c r="E77" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77">
+        <v>63</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="W77">
+        <v>1</v>
+      </c>
+      <c r="AD77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6588,8 +8107,26 @@
       <c r="E78" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78">
+        <v>73</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+      <c r="AD78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6606,7 +8143,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:30">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6622,8 +8159,29 @@
       <c r="E80" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80">
+        <v>70</v>
+      </c>
+      <c r="G80">
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="N80" t="s">
+        <v>509</v>
+      </c>
+      <c r="O80" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6639,8 +8197,32 @@
       <c r="E81" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81">
+        <v>51</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="V81">
+        <v>1</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="AD81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6656,8 +8238,26 @@
       <c r="E82" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82">
+        <v>69</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+      <c r="AB82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6674,7 +8274,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:30">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6690,8 +8290,29 @@
       <c r="E84" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84">
+        <v>80</v>
+      </c>
+      <c r="J84">
+        <v>1</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="N84" t="s">
+        <v>509</v>
+      </c>
+      <c r="O84" t="s">
+        <v>510</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="X84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6707,8 +8328,29 @@
       <c r="E85" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85">
+        <v>61</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="S85">
+        <v>1</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+      <c r="AC85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6725,7 +8367,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:30">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6741,8 +8383,29 @@
       <c r="E87" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87">
+        <v>65</v>
+      </c>
+      <c r="G87">
+        <v>7</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="Q87">
+        <v>1</v>
+      </c>
+      <c r="V87">
+        <v>1</v>
+      </c>
+      <c r="AB87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6758,8 +8421,32 @@
       <c r="E88" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88">
+        <v>65</v>
+      </c>
+      <c r="G88">
+        <v>7</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="N88" t="s">
+        <v>509</v>
+      </c>
+      <c r="O88" t="s">
+        <v>511</v>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="AD88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6775,8 +8462,29 @@
       <c r="E89" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89">
+        <v>68</v>
+      </c>
+      <c r="G89">
+        <v>7</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="S89">
+        <v>1</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="AB89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6792,8 +8500,29 @@
       <c r="E90" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90">
+        <v>65</v>
+      </c>
+      <c r="G90">
+        <v>5</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="P90">
+        <v>1</v>
+      </c>
+      <c r="V90">
+        <v>1</v>
+      </c>
+      <c r="AC90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6809,8 +8538,32 @@
       <c r="E91" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91">
+        <v>65</v>
+      </c>
+      <c r="G91">
+        <v>5</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="Q91">
+        <v>1</v>
+      </c>
+      <c r="V91">
+        <v>1</v>
+      </c>
+      <c r="X91">
+        <v>1</v>
+      </c>
+      <c r="Z91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6826,8 +8579,23 @@
       <c r="E92" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92">
+        <v>65</v>
+      </c>
+      <c r="G92">
+        <v>7</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="T92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6843,8 +8611,20 @@
       <c r="E93" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93">
+        <v>63</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="L93">
+        <v>1</v>
+      </c>
+      <c r="V93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6860,8 +8640,26 @@
       <c r="E94" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94">
+        <v>55</v>
+      </c>
+      <c r="G94">
+        <v>4</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94">
+        <v>1</v>
+      </c>
+      <c r="V94">
+        <v>1</v>
+      </c>
+      <c r="AC94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6878,7 +8676,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:30">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6894,8 +8692,20 @@
       <c r="E96" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96">
+        <v>70</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96" t="s">
+        <v>512</v>
+      </c>
+      <c r="O96" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6911,8 +8721,29 @@
       <c r="E97" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97">
+        <v>65</v>
+      </c>
+      <c r="G97">
+        <v>4</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+      <c r="V97">
+        <v>1</v>
+      </c>
+      <c r="X97">
+        <v>1</v>
+      </c>
+      <c r="AB97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6928,8 +8759,23 @@
       <c r="E98" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98">
+        <v>47</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="L98">
+        <v>1</v>
+      </c>
+      <c r="T98">
+        <v>1</v>
+      </c>
+      <c r="AC98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6945,8 +8791,26 @@
       <c r="E99" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99">
+        <v>53</v>
+      </c>
+      <c r="G99">
+        <v>5</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="L99">
+        <v>1</v>
+      </c>
+      <c r="T99">
+        <v>1</v>
+      </c>
+      <c r="AD99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6962,8 +8826,23 @@
       <c r="E100" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100">
+        <v>31</v>
+      </c>
+      <c r="G100">
+        <v>7</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="L100">
+        <v>1</v>
+      </c>
+      <c r="S100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6979,8 +8858,29 @@
       <c r="E101" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101">
+        <v>45</v>
+      </c>
+      <c r="G101">
+        <v>5</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="L101">
+        <v>1</v>
+      </c>
+      <c r="T101">
+        <v>1</v>
+      </c>
+      <c r="X101">
+        <v>1</v>
+      </c>
+      <c r="AC101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6996,8 +8896,26 @@
       <c r="E102" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102">
+        <v>66</v>
+      </c>
+      <c r="G102">
+        <v>5</v>
+      </c>
+      <c r="I102">
+        <v>1</v>
+      </c>
+      <c r="L102">
+        <v>1</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
+      </c>
+      <c r="X102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7014,7 +8932,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:30">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7030,8 +8948,26 @@
       <c r="E104" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104">
+        <v>63</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="T104">
+        <v>1</v>
+      </c>
+      <c r="AD104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7048,7 +8984,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:30">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7064,8 +9000,29 @@
       <c r="E106" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106">
+        <v>76</v>
+      </c>
+      <c r="G106">
+        <v>7</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="L106">
+        <v>1</v>
+      </c>
+      <c r="T106">
+        <v>3</v>
+      </c>
+      <c r="X106">
+        <v>1</v>
+      </c>
+      <c r="AD106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7082,7 +9039,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:30">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7098,8 +9055,35 @@
       <c r="E108" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108">
+        <v>68</v>
+      </c>
+      <c r="G108">
+        <v>6</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="M108">
+        <v>1</v>
+      </c>
+      <c r="N108" t="s">
+        <v>512</v>
+      </c>
+      <c r="O108" t="s">
+        <v>513</v>
+      </c>
+      <c r="T108">
+        <v>1</v>
+      </c>
+      <c r="X108">
+        <v>1</v>
+      </c>
+      <c r="AD108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7115,8 +9099,26 @@
       <c r="E109" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109">
+        <v>70</v>
+      </c>
+      <c r="G109">
+        <v>2</v>
+      </c>
+      <c r="I109">
+        <v>1</v>
+      </c>
+      <c r="L109">
+        <v>1</v>
+      </c>
+      <c r="T109">
+        <v>1</v>
+      </c>
+      <c r="AD109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7132,8 +9134,29 @@
       <c r="E110" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110">
+        <v>70</v>
+      </c>
+      <c r="G110">
+        <v>7</v>
+      </c>
+      <c r="I110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="T110">
+        <v>1</v>
+      </c>
+      <c r="X110">
+        <v>1</v>
+      </c>
+      <c r="AD110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7149,8 +9172,23 @@
       <c r="E111" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111">
+        <v>61</v>
+      </c>
+      <c r="G111">
+        <v>4</v>
+      </c>
+      <c r="K111">
+        <v>1</v>
+      </c>
+      <c r="P111">
+        <v>1</v>
+      </c>
+      <c r="V111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7166,8 +9204,29 @@
       <c r="E112" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112">
+        <v>56</v>
+      </c>
+      <c r="G112">
+        <v>7</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="L112">
+        <v>1</v>
+      </c>
+      <c r="U112">
+        <v>1</v>
+      </c>
+      <c r="X112">
+        <v>1</v>
+      </c>
+      <c r="AC112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7183,8 +9242,26 @@
       <c r="E113" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113">
+        <v>74</v>
+      </c>
+      <c r="I113">
+        <v>1</v>
+      </c>
+      <c r="L113">
+        <v>1</v>
+      </c>
+      <c r="T113">
+        <v>1</v>
+      </c>
+      <c r="X113">
+        <v>1</v>
+      </c>
+      <c r="AD113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7200,8 +9277,29 @@
       <c r="E114" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="G114">
+        <v>3</v>
+      </c>
+      <c r="I114">
+        <v>1</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="U114">
+        <v>1</v>
+      </c>
+      <c r="V114">
+        <v>1</v>
+      </c>
+      <c r="X114">
+        <v>1</v>
+      </c>
+      <c r="AC114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7217,8 +9315,23 @@
       <c r="E115" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="F115">
+        <v>70</v>
+      </c>
+      <c r="I115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="T115">
+        <v>1</v>
+      </c>
+      <c r="AD115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:30">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7234,8 +9347,26 @@
       <c r="E116" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116">
+        <v>67</v>
+      </c>
+      <c r="J116">
+        <v>1</v>
+      </c>
+      <c r="M116">
+        <v>1</v>
+      </c>
+      <c r="Q116">
+        <v>1</v>
+      </c>
+      <c r="X116">
+        <v>1</v>
+      </c>
+      <c r="AD116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:30">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7252,7 +9383,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:30">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7268,8 +9399,26 @@
       <c r="E118" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118">
+        <v>47</v>
+      </c>
+      <c r="G118">
+        <v>7</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="L118">
+        <v>1</v>
+      </c>
+      <c r="T118">
+        <v>1</v>
+      </c>
+      <c r="AD118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:30">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7285,8 +9434,23 @@
       <c r="E119" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119">
+        <v>38</v>
+      </c>
+      <c r="G119">
+        <v>5</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="M119">
+        <v>1</v>
+      </c>
+      <c r="AB119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:30">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7302,8 +9466,20 @@
       <c r="E120" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="F120">
+        <v>78</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="T120">
+        <v>1</v>
+      </c>
+      <c r="X120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:30">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7319,8 +9495,29 @@
       <c r="E121" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121">
+        <v>47</v>
+      </c>
+      <c r="G121">
+        <v>6</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>1</v>
+      </c>
+      <c r="T121">
+        <v>1</v>
+      </c>
+      <c r="X121">
+        <v>1</v>
+      </c>
+      <c r="AD121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:30">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7336,8 +9533,32 @@
       <c r="E122" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122">
+        <v>66</v>
+      </c>
+      <c r="G122">
+        <v>8</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="L122">
+        <v>1</v>
+      </c>
+      <c r="R122">
+        <v>1</v>
+      </c>
+      <c r="V122">
+        <v>1</v>
+      </c>
+      <c r="X122">
+        <v>1</v>
+      </c>
+      <c r="AD122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:30">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7353,8 +9574,32 @@
       <c r="E123" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123">
+        <v>62</v>
+      </c>
+      <c r="G123">
+        <v>5</v>
+      </c>
+      <c r="H123">
+        <v>1</v>
+      </c>
+      <c r="M123">
+        <v>1</v>
+      </c>
+      <c r="Q123">
+        <v>1</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="Y123">
+        <v>1</v>
+      </c>
+      <c r="Z123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:30">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7370,8 +9615,26 @@
       <c r="E124" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124">
+        <v>69</v>
+      </c>
+      <c r="G124">
+        <v>7</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="L124">
+        <v>1</v>
+      </c>
+      <c r="T124">
+        <v>1</v>
+      </c>
+      <c r="AD124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:30">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7387,8 +9650,23 @@
       <c r="E125" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125">
+        <v>74</v>
+      </c>
+      <c r="G125">
+        <v>3</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="L125">
+        <v>1</v>
+      </c>
+      <c r="S125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:30">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7405,7 +9683,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:30">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7422,7 +9700,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:30">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7439,7 +9717,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:30">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7455,8 +9733,32 @@
       <c r="E129" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129">
+        <v>64</v>
+      </c>
+      <c r="G129">
+        <v>5</v>
+      </c>
+      <c r="I129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>1</v>
+      </c>
+      <c r="Q129">
+        <v>1</v>
+      </c>
+      <c r="V129">
+        <v>1</v>
+      </c>
+      <c r="X129">
+        <v>1</v>
+      </c>
+      <c r="AC129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:30">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7472,8 +9774,23 @@
       <c r="E130" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130">
+        <v>50</v>
+      </c>
+      <c r="G130">
+        <v>5</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="AD130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:30">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7489,8 +9806,29 @@
       <c r="E131" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131">
+        <v>76</v>
+      </c>
+      <c r="G131">
+        <v>3</v>
+      </c>
+      <c r="I131">
+        <v>1</v>
+      </c>
+      <c r="L131">
+        <v>1</v>
+      </c>
+      <c r="S131">
+        <v>1</v>
+      </c>
+      <c r="X131">
+        <v>1</v>
+      </c>
+      <c r="AA131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:30">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7506,8 +9844,26 @@
       <c r="E132" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132">
+        <v>78</v>
+      </c>
+      <c r="G132">
+        <v>2</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="T132">
+        <v>1</v>
+      </c>
+      <c r="X132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:30">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7523,8 +9879,26 @@
       <c r="E133" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133">
+        <v>54</v>
+      </c>
+      <c r="G133">
+        <v>4</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="U133">
+        <v>1</v>
+      </c>
+      <c r="X133">
+        <v>1</v>
+      </c>
+      <c r="AD133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:30">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7540,8 +9914,29 @@
       <c r="E134" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134">
+        <v>45</v>
+      </c>
+      <c r="G134">
+        <v>7</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>1</v>
+      </c>
+      <c r="T134">
+        <v>1</v>
+      </c>
+      <c r="X134">
+        <v>1</v>
+      </c>
+      <c r="AD134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:30">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7558,7 +9953,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:30">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7574,8 +9969,23 @@
       <c r="E136" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136">
+        <v>68</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>1</v>
+      </c>
+      <c r="S136">
+        <v>1</v>
+      </c>
+      <c r="X136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:30">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7591,8 +10001,26 @@
       <c r="E137" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137">
+        <v>61</v>
+      </c>
+      <c r="G137">
+        <v>3</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="S137">
+        <v>1</v>
+      </c>
+      <c r="AC137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:30">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7609,7 +10037,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:30">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7626,7 +10054,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:30">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7642,8 +10070,29 @@
       <c r="E140" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140">
+        <v>61</v>
+      </c>
+      <c r="G140">
+        <v>3</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="Q140">
+        <v>1</v>
+      </c>
+      <c r="W140">
+        <v>1</v>
+      </c>
+      <c r="Z140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:30">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7659,8 +10108,29 @@
       <c r="E141" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141">
+        <v>67</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="T141">
+        <v>1</v>
+      </c>
+      <c r="V141">
+        <v>1</v>
+      </c>
+      <c r="X141">
+        <v>1</v>
+      </c>
+      <c r="AD141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:30">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7676,8 +10146,29 @@
       <c r="E142" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142">
+        <v>68</v>
+      </c>
+      <c r="G142">
+        <v>6</v>
+      </c>
+      <c r="I142">
+        <v>1</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="T142">
+        <v>1</v>
+      </c>
+      <c r="X142">
+        <v>1</v>
+      </c>
+      <c r="AA142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:30">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7694,7 +10185,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:30">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7710,8 +10201,32 @@
       <c r="E144" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144">
+        <v>62</v>
+      </c>
+      <c r="G144">
+        <v>5</v>
+      </c>
+      <c r="I144">
+        <v>1</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="T144">
+        <v>1</v>
+      </c>
+      <c r="V144">
+        <v>1</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+      <c r="AC144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:29">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7727,8 +10242,23 @@
       <c r="E145" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145">
+        <v>78</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="I145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="T145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:29">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7745,7 +10275,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:29">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7761,8 +10291,29 @@
       <c r="E147" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147">
+        <v>71</v>
+      </c>
+      <c r="G147">
+        <v>3</v>
+      </c>
+      <c r="J147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>1</v>
+      </c>
+      <c r="T147">
+        <v>1</v>
+      </c>
+      <c r="X147">
+        <v>1</v>
+      </c>
+      <c r="AB147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:29">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7778,8 +10329,26 @@
       <c r="E148" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148">
+        <v>52</v>
+      </c>
+      <c r="G148">
+        <v>7</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="T148">
+        <v>1</v>
+      </c>
+      <c r="Z148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:29">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7795,8 +10364,23 @@
       <c r="E149" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149">
+        <v>57</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="Q149">
+        <v>1</v>
+      </c>
+      <c r="AB149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7812,8 +10396,29 @@
       <c r="E150" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150">
+        <v>56</v>
+      </c>
+      <c r="G150">
+        <v>4</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="T150">
+        <v>1</v>
+      </c>
+      <c r="X150">
+        <v>1</v>
+      </c>
+      <c r="AC150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:29">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7830,7 +10435,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:29">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7846,8 +10451,20 @@
       <c r="E152" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152">
+        <v>83</v>
+      </c>
+      <c r="G152">
+        <v>2</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="U152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:29">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7863,8 +10480,29 @@
       <c r="E153" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153">
+        <v>60</v>
+      </c>
+      <c r="G153">
+        <v>4</v>
+      </c>
+      <c r="I153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>1</v>
+      </c>
+      <c r="T153">
+        <v>1</v>
+      </c>
+      <c r="X153">
+        <v>1</v>
+      </c>
+      <c r="AC153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:29">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7880,8 +10518,23 @@
       <c r="E154" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154">
+        <v>62</v>
+      </c>
+      <c r="H154">
+        <v>1</v>
+      </c>
+      <c r="P154">
+        <v>1</v>
+      </c>
+      <c r="W154">
+        <v>1</v>
+      </c>
+      <c r="AC154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:29">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7897,8 +10550,29 @@
       <c r="E155" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155">
+        <v>70</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="Q155">
+        <v>1</v>
+      </c>
+      <c r="V155">
+        <v>1</v>
+      </c>
+      <c r="X155">
+        <v>1</v>
+      </c>
+      <c r="AB155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:29">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7914,8 +10588,29 @@
       <c r="E156" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156">
+        <v>53</v>
+      </c>
+      <c r="G156">
+        <v>6</v>
+      </c>
+      <c r="H156">
+        <v>1</v>
+      </c>
+      <c r="L156">
+        <v>1</v>
+      </c>
+      <c r="T156">
+        <v>1</v>
+      </c>
+      <c r="X156">
+        <v>1</v>
+      </c>
+      <c r="AC156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:29">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7932,7 +10627,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:29">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7948,8 +10643,26 @@
       <c r="E158" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158">
+        <v>63</v>
+      </c>
+      <c r="G158">
+        <v>5</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>1</v>
+      </c>
+      <c r="P158">
+        <v>1</v>
+      </c>
+      <c r="W158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:29">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7965,8 +10678,29 @@
       <c r="E159" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159">
+        <v>64</v>
+      </c>
+      <c r="G159">
+        <v>4</v>
+      </c>
+      <c r="H159">
+        <v>1</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+      <c r="P159">
+        <v>1</v>
+      </c>
+      <c r="V159">
+        <v>1</v>
+      </c>
+      <c r="AC159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:29">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7982,8 +10716,29 @@
       <c r="E160" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160">
+        <v>78</v>
+      </c>
+      <c r="G160">
+        <v>4</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="S160">
+        <v>1</v>
+      </c>
+      <c r="V160">
+        <v>1</v>
+      </c>
+      <c r="X160">
+        <v>1</v>
+      </c>
+      <c r="AA160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:29">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7999,8 +10754,32 @@
       <c r="E161" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161">
+        <v>60</v>
+      </c>
+      <c r="G161">
+        <v>4</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>1</v>
+      </c>
+      <c r="Q161">
+        <v>1</v>
+      </c>
+      <c r="V161">
+        <v>1</v>
+      </c>
+      <c r="X161">
+        <v>1</v>
+      </c>
+      <c r="AB161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:29">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8017,7 +10796,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:29">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8033,8 +10812,17 @@
       <c r="E163" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163">
+        <v>77</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="S163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:29">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8050,8 +10838,26 @@
       <c r="E164" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164">
+        <v>57</v>
+      </c>
+      <c r="J164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="Q164">
+        <v>1</v>
+      </c>
+      <c r="V164">
+        <v>1</v>
+      </c>
+      <c r="AA164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:29">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8067,8 +10873,29 @@
       <c r="E165" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165">
+        <v>66</v>
+      </c>
+      <c r="G165">
+        <v>4</v>
+      </c>
+      <c r="I165">
+        <v>1</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="T165">
+        <v>1</v>
+      </c>
+      <c r="X165">
+        <v>1</v>
+      </c>
+      <c r="AB165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:29">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8084,8 +10911,29 @@
       <c r="E166" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166">
+        <v>64</v>
+      </c>
+      <c r="G166">
+        <v>4</v>
+      </c>
+      <c r="I166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="Q166">
+        <v>1</v>
+      </c>
+      <c r="V166">
+        <v>1</v>
+      </c>
+      <c r="AC166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:29">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8101,8 +10949,26 @@
       <c r="E167" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167">
+        <v>65</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="T167">
+        <v>1</v>
+      </c>
+      <c r="Y167">
+        <v>1</v>
+      </c>
+      <c r="AB167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:29">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8118,8 +10984,29 @@
       <c r="E168" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168">
+        <v>44</v>
+      </c>
+      <c r="G168">
+        <v>5</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="Q168">
+        <v>1</v>
+      </c>
+      <c r="W168">
+        <v>1</v>
+      </c>
+      <c r="AB168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:29">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8136,7 +11023,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:29">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8153,7 +11040,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:29">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8169,8 +11056,29 @@
       <c r="E171" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171">
+        <v>54</v>
+      </c>
+      <c r="G171">
+        <v>4</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="P171">
+        <v>1</v>
+      </c>
+      <c r="V171">
+        <v>1</v>
+      </c>
+      <c r="AB171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:29">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8186,8 +11094,32 @@
       <c r="E172" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172">
+        <v>63</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="O172" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q172">
+        <v>1</v>
+      </c>
+      <c r="V172">
+        <v>1</v>
+      </c>
+      <c r="X172">
+        <v>1</v>
+      </c>
+      <c r="AB172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:29">
       <c r="A173">
         <v>172</v>
       </c>
@@ -8203,8 +11135,32 @@
       <c r="E173" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173">
+        <v>68</v>
+      </c>
+      <c r="G173">
+        <v>3</v>
+      </c>
+      <c r="H173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+      <c r="R173">
+        <v>1</v>
+      </c>
+      <c r="T173">
+        <v>1</v>
+      </c>
+      <c r="V173">
+        <v>1</v>
+      </c>
+      <c r="X173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:29">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8221,7 +11177,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:29">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8237,8 +11193,29 @@
       <c r="E175" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175">
+        <v>70</v>
+      </c>
+      <c r="G175">
+        <v>2</v>
+      </c>
+      <c r="M175">
+        <v>1</v>
+      </c>
+      <c r="N175" t="s">
+        <v>507</v>
+      </c>
+      <c r="O175" t="s">
+        <v>508</v>
+      </c>
+      <c r="Y175">
+        <v>1</v>
+      </c>
+      <c r="Z175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:29">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8255,7 +11232,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:30">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8272,7 +11249,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:30">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8288,8 +11265,26 @@
       <c r="E178" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178">
+        <v>70</v>
+      </c>
+      <c r="G178">
+        <v>2</v>
+      </c>
+      <c r="I178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>1</v>
+      </c>
+      <c r="Q178">
+        <v>1</v>
+      </c>
+      <c r="AD178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:30">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8305,8 +11300,26 @@
       <c r="E179" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="F179">
+        <v>49</v>
+      </c>
+      <c r="G179">
+        <v>6</v>
+      </c>
+      <c r="I179">
+        <v>1</v>
+      </c>
+      <c r="M179">
+        <v>1</v>
+      </c>
+      <c r="U179">
+        <v>1</v>
+      </c>
+      <c r="AC179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:30">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8323,7 +11336,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:30">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8340,7 +11353,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:30">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8357,7 +11370,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:30">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8374,7 +11387,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:30">
       <c r="A184">
         <v>183</v>
       </c>
@@ -8390,8 +11403,29 @@
       <c r="E184" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="F184">
+        <v>59</v>
+      </c>
+      <c r="I184">
+        <v>1</v>
+      </c>
+      <c r="M184">
+        <v>1</v>
+      </c>
+      <c r="N184" t="s">
+        <v>507</v>
+      </c>
+      <c r="O184" t="s">
+        <v>508</v>
+      </c>
+      <c r="U184">
+        <v>1</v>
+      </c>
+      <c r="AC184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:30">
       <c r="A185">
         <v>184</v>
       </c>
@@ -8407,8 +11441,32 @@
       <c r="E185" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="F185">
+        <v>78</v>
+      </c>
+      <c r="G185">
+        <v>4</v>
+      </c>
+      <c r="I185">
+        <v>1</v>
+      </c>
+      <c r="L185">
+        <v>1</v>
+      </c>
+      <c r="T185">
+        <v>1</v>
+      </c>
+      <c r="V185">
+        <v>1</v>
+      </c>
+      <c r="X185">
+        <v>1</v>
+      </c>
+      <c r="AA185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:30">
       <c r="A186">
         <v>185</v>
       </c>
@@ -8424,8 +11482,32 @@
       <c r="E186" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="F186">
+        <v>89</v>
+      </c>
+      <c r="G186">
+        <v>2</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="T186">
+        <v>1</v>
+      </c>
+      <c r="V186">
+        <v>1</v>
+      </c>
+      <c r="X186">
+        <v>1</v>
+      </c>
+      <c r="AA186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:30">
       <c r="A187">
         <v>186</v>
       </c>
@@ -8441,8 +11523,29 @@
       <c r="E187" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="F187">
+        <v>51</v>
+      </c>
+      <c r="G187">
+        <v>2</v>
+      </c>
+      <c r="I187">
+        <v>1</v>
+      </c>
+      <c r="L187">
+        <v>1</v>
+      </c>
+      <c r="U187">
+        <v>1</v>
+      </c>
+      <c r="X187">
+        <v>1</v>
+      </c>
+      <c r="AC187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:30">
       <c r="A188">
         <v>187</v>
       </c>
@@ -8458,8 +11561,29 @@
       <c r="E188" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="F188">
+        <v>78</v>
+      </c>
+      <c r="G188">
+        <v>5</v>
+      </c>
+      <c r="I188">
+        <v>1</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>1</v>
+      </c>
+      <c r="X188">
+        <v>1</v>
+      </c>
+      <c r="AD188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:30">
       <c r="A189">
         <v>188</v>
       </c>
@@ -8475,8 +11599,35 @@
       <c r="E189" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="F189">
+        <v>45</v>
+      </c>
+      <c r="G189">
+        <v>5</v>
+      </c>
+      <c r="J189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="Q189">
+        <v>1</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="W189">
+        <v>1</v>
+      </c>
+      <c r="X189">
+        <v>1</v>
+      </c>
+      <c r="Z189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:30">
       <c r="A190">
         <v>189</v>
       </c>
@@ -8493,7 +11644,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:30">
       <c r="A191">
         <v>190</v>
       </c>
@@ -8509,8 +11660,20 @@
       <c r="E191" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="F191">
+        <v>76</v>
+      </c>
+      <c r="G191">
+        <v>2</v>
+      </c>
+      <c r="I191">
+        <v>1</v>
+      </c>
+      <c r="U191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:30">
       <c r="A192">
         <v>191</v>
       </c>
@@ -8526,8 +11689,32 @@
       <c r="E192" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="F192">
+        <v>59</v>
+      </c>
+      <c r="G192">
+        <v>3</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>1</v>
+      </c>
+      <c r="N192" t="s">
+        <v>507</v>
+      </c>
+      <c r="O192" t="s">
+        <v>508</v>
+      </c>
+      <c r="T192">
+        <v>1</v>
+      </c>
+      <c r="AD192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:30">
       <c r="A193">
         <v>192</v>
       </c>
@@ -8544,7 +11731,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:30">
       <c r="A194">
         <v>193</v>
       </c>
@@ -8560,8 +11747,26 @@
       <c r="E194" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="195" spans="1:5">
+      <c r="F194">
+        <v>52</v>
+      </c>
+      <c r="G194">
+        <v>2</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="L194">
+        <v>1</v>
+      </c>
+      <c r="S194">
+        <v>1</v>
+      </c>
+      <c r="X194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:30">
       <c r="A195">
         <v>194</v>
       </c>
@@ -8578,7 +11783,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:30">
       <c r="A196">
         <v>195</v>
       </c>
@@ -8594,8 +11799,26 @@
       <c r="E196" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="197" spans="1:5">
+      <c r="F196">
+        <v>81</v>
+      </c>
+      <c r="G196">
+        <v>2</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196" t="s">
+        <v>515</v>
+      </c>
+      <c r="O196" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="197" spans="1:30">
       <c r="A197">
         <v>196</v>
       </c>
@@ -8612,7 +11835,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:30">
       <c r="A198">
         <v>197</v>
       </c>
@@ -8628,25 +11851,44 @@
       <c r="E198" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="199" spans="1:5">
-      <c r="A199">
+      <c r="F198">
+        <v>65</v>
+      </c>
+      <c r="G198">
+        <v>3</v>
+      </c>
+      <c r="M198">
+        <v>1</v>
+      </c>
+      <c r="N198" t="s">
+        <v>515</v>
+      </c>
+      <c r="O198" t="s">
+        <v>516</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:30">
+      <c r="A199" s="1">
         <v>198</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="1">
         <v>40</v>
       </c>
-      <c r="C199" t="s">
+      <c r="C199" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D199" t="s">
-        <v>1</v>
-      </c>
-      <c r="E199" t="s">
+      <c r="D199" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E199" s="1" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="200" spans="1:5">
+      <c r="F199" s="1"/>
+    </row>
+    <row r="200" spans="1:30">
       <c r="A200">
         <v>199</v>
       </c>
@@ -8662,8 +11904,29 @@
       <c r="E200" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="201" spans="1:5">
+      <c r="F200">
+        <v>42</v>
+      </c>
+      <c r="G200">
+        <v>5</v>
+      </c>
+      <c r="I200">
+        <v>1</v>
+      </c>
+      <c r="L200">
+        <v>1</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="X200">
+        <v>1</v>
+      </c>
+      <c r="AD200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:30">
       <c r="A201">
         <v>200</v>
       </c>
@@ -8679,8 +11942,26 @@
       <c r="E201" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="202" spans="1:5">
+      <c r="F201">
+        <v>76</v>
+      </c>
+      <c r="G201">
+        <v>6</v>
+      </c>
+      <c r="J201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201" t="s">
+        <v>507</v>
+      </c>
+      <c r="O201" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="202" spans="1:30">
       <c r="A202">
         <v>201</v>
       </c>
@@ -8696,8 +11977,26 @@
       <c r="E202" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="203" spans="1:5">
+      <c r="F202">
+        <v>45</v>
+      </c>
+      <c r="G202">
+        <v>6</v>
+      </c>
+      <c r="I202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="Z202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:30">
       <c r="A203">
         <v>202</v>
       </c>
@@ -8713,8 +12012,32 @@
       <c r="E203" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="204" spans="1:5">
+      <c r="F203">
+        <v>61</v>
+      </c>
+      <c r="G203">
+        <v>9</v>
+      </c>
+      <c r="H203">
+        <v>1</v>
+      </c>
+      <c r="L203">
+        <v>1</v>
+      </c>
+      <c r="T203">
+        <v>1</v>
+      </c>
+      <c r="V203">
+        <v>1</v>
+      </c>
+      <c r="X203">
+        <v>1</v>
+      </c>
+      <c r="AD203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:30">
       <c r="A204">
         <v>203</v>
       </c>
@@ -8731,7 +12054,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:30">
       <c r="A205">
         <v>204</v>
       </c>
@@ -8747,8 +12070,26 @@
       <c r="E205" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="206" spans="1:5">
+      <c r="F205">
+        <v>81</v>
+      </c>
+      <c r="I205">
+        <v>1</v>
+      </c>
+      <c r="M205">
+        <v>1</v>
+      </c>
+      <c r="N205" t="s">
+        <v>509</v>
+      </c>
+      <c r="O205" t="s">
+        <v>511</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:30">
       <c r="A206">
         <v>205</v>
       </c>
@@ -8764,8 +12105,26 @@
       <c r="E206" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="F206">
+        <v>59</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="L206">
+        <v>1</v>
+      </c>
+      <c r="U206">
+        <v>1</v>
+      </c>
+      <c r="X206">
+        <v>1</v>
+      </c>
+      <c r="AC206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:30">
       <c r="A207">
         <v>206</v>
       </c>
@@ -8781,8 +12140,29 @@
       <c r="E207" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="F207">
+        <v>69</v>
+      </c>
+      <c r="G207">
+        <v>5</v>
+      </c>
+      <c r="I207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>1</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="X207">
+        <v>1</v>
+      </c>
+      <c r="AC207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:30">
       <c r="A208">
         <v>207</v>
       </c>
@@ -8799,7 +12179,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:30">
       <c r="A209">
         <v>208</v>
       </c>
@@ -8816,7 +12196,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:30">
       <c r="A210">
         <v>209</v>
       </c>
@@ -8833,7 +12213,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:30">
       <c r="A211">
         <v>210</v>
       </c>
@@ -8850,7 +12230,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:30">
       <c r="A212">
         <v>211</v>
       </c>
@@ -8866,8 +12246,32 @@
       <c r="E212" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="F212">
+        <v>41</v>
+      </c>
+      <c r="G212">
+        <v>6</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="N212" t="s">
+        <v>512</v>
+      </c>
+      <c r="O212" t="s">
+        <v>517</v>
+      </c>
+      <c r="T212">
+        <v>1</v>
+      </c>
+      <c r="AD212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:30">
       <c r="A213">
         <v>212</v>
       </c>
@@ -8883,8 +12287,26 @@
       <c r="E213" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="F213">
+        <v>45</v>
+      </c>
+      <c r="G213">
+        <v>2</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="L213">
+        <v>1</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="AD213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:30">
       <c r="A214">
         <v>213</v>
       </c>
@@ -8901,7 +12323,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:30">
       <c r="A215">
         <v>214</v>
       </c>
@@ -8918,7 +12340,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:30">
       <c r="A216">
         <v>215</v>
       </c>
@@ -8934,8 +12356,29 @@
       <c r="E216" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="F216">
+        <v>59</v>
+      </c>
+      <c r="G216">
+        <v>7</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>1</v>
+      </c>
+      <c r="U216">
+        <v>1</v>
+      </c>
+      <c r="X216">
+        <v>1</v>
+      </c>
+      <c r="AD216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:30">
       <c r="A217">
         <v>216</v>
       </c>
@@ -8951,8 +12394,29 @@
       <c r="E217" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="F217">
+        <v>55</v>
+      </c>
+      <c r="G217">
+        <v>5</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="T217">
+        <v>1</v>
+      </c>
+      <c r="X217">
+        <v>1</v>
+      </c>
+      <c r="Z217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:30">
       <c r="A218">
         <v>217</v>
       </c>
@@ -8969,7 +12433,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:30">
       <c r="A219">
         <v>218</v>
       </c>
@@ -8986,7 +12450,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:30">
       <c r="A220">
         <v>219</v>
       </c>
@@ -9003,7 +12467,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:30">
       <c r="A221">
         <v>220</v>
       </c>
@@ -9020,7 +12484,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:30">
       <c r="A222">
         <v>221</v>
       </c>
@@ -9037,7 +12501,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:30">
       <c r="A223">
         <v>222</v>
       </c>
@@ -9054,7 +12518,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:30">
       <c r="A224">
         <v>223</v>
       </c>
@@ -9070,8 +12534,32 @@
       <c r="E224" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="F224">
+        <v>65</v>
+      </c>
+      <c r="G224">
+        <v>3</v>
+      </c>
+      <c r="I224">
+        <v>1</v>
+      </c>
+      <c r="L224">
+        <v>1</v>
+      </c>
+      <c r="T224">
+        <v>1</v>
+      </c>
+      <c r="V224">
+        <v>1</v>
+      </c>
+      <c r="X224">
+        <v>1</v>
+      </c>
+      <c r="AD224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:30">
       <c r="A225">
         <v>224</v>
       </c>
@@ -9087,8 +12575,32 @@
       <c r="E225" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="F225">
+        <v>55</v>
+      </c>
+      <c r="G225">
+        <v>6</v>
+      </c>
+      <c r="H225">
+        <v>1</v>
+      </c>
+      <c r="L225">
+        <v>1</v>
+      </c>
+      <c r="T225">
+        <v>1</v>
+      </c>
+      <c r="V225">
+        <v>1</v>
+      </c>
+      <c r="X225">
+        <v>1</v>
+      </c>
+      <c r="AC225">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:30">
       <c r="A226">
         <v>225</v>
       </c>
@@ -9104,8 +12616,35 @@
       <c r="E226" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="F226">
+        <v>58</v>
+      </c>
+      <c r="G226">
+        <v>4</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="M226">
+        <v>1</v>
+      </c>
+      <c r="N226" t="s">
+        <v>509</v>
+      </c>
+      <c r="O226" t="s">
+        <v>518</v>
+      </c>
+      <c r="U226">
+        <v>1</v>
+      </c>
+      <c r="X226">
+        <v>1</v>
+      </c>
+      <c r="Z226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:30">
       <c r="A227">
         <v>226</v>
       </c>
@@ -9121,8 +12660,29 @@
       <c r="E227" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="F227">
+        <v>57</v>
+      </c>
+      <c r="G227">
+        <v>8</v>
+      </c>
+      <c r="H227">
+        <v>1</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="P227">
+        <v>1</v>
+      </c>
+      <c r="W227">
+        <v>1</v>
+      </c>
+      <c r="Z227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:30">
       <c r="A228">
         <v>227</v>
       </c>
@@ -9138,8 +12698,29 @@
       <c r="E228" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="F228">
+        <v>48</v>
+      </c>
+      <c r="G228">
+        <v>3</v>
+      </c>
+      <c r="I228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>1</v>
+      </c>
+      <c r="Q228">
+        <v>1</v>
+      </c>
+      <c r="U228">
+        <v>1</v>
+      </c>
+      <c r="AC228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:30">
       <c r="A229">
         <v>228</v>
       </c>
@@ -9155,8 +12736,26 @@
       <c r="E229" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="F229">
+        <v>43</v>
+      </c>
+      <c r="H229">
+        <v>1</v>
+      </c>
+      <c r="K229">
+        <v>1</v>
+      </c>
+      <c r="P229">
+        <v>1</v>
+      </c>
+      <c r="W229">
+        <v>1</v>
+      </c>
+      <c r="AA229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:30">
       <c r="A230">
         <v>229</v>
       </c>
@@ -9172,8 +12771,17 @@
       <c r="E230" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="F230">
+        <v>65</v>
+      </c>
+      <c r="G230">
+        <v>7</v>
+      </c>
+      <c r="H230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:30">
       <c r="A231">
         <v>230</v>
       </c>
@@ -9190,7 +12798,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:30">
       <c r="A232">
         <v>231</v>
       </c>
@@ -9206,8 +12814,23 @@
       <c r="E232" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="F232">
+        <v>65</v>
+      </c>
+      <c r="G232">
+        <v>2</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+      <c r="Q232">
+        <v>1</v>
+      </c>
+      <c r="Z232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:30">
       <c r="A233">
         <v>232</v>
       </c>
@@ -9224,7 +12847,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:30">
       <c r="A234">
         <v>233</v>
       </c>
@@ -9240,8 +12863,20 @@
       <c r="E234" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="F234">
+        <v>64</v>
+      </c>
+      <c r="G234">
+        <v>4</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="Q234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:30">
       <c r="A235">
         <v>234</v>
       </c>
@@ -9258,7 +12893,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:30">
       <c r="A236">
         <v>235</v>
       </c>
@@ -9274,8 +12909,32 @@
       <c r="E236" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="F236">
+        <v>31</v>
+      </c>
+      <c r="G236">
+        <v>4</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="P236">
+        <v>1</v>
+      </c>
+      <c r="V236">
+        <v>1</v>
+      </c>
+      <c r="X236">
+        <v>1</v>
+      </c>
+      <c r="AC236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:30">
       <c r="A237">
         <v>236</v>
       </c>
@@ -9292,7 +12951,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:30">
       <c r="A238">
         <v>237</v>
       </c>
@@ -9308,8 +12967,32 @@
       <c r="E238" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="F238">
+        <v>52</v>
+      </c>
+      <c r="G238">
+        <v>2</v>
+      </c>
+      <c r="H238">
+        <v>1</v>
+      </c>
+      <c r="K238">
+        <v>1</v>
+      </c>
+      <c r="Q238">
+        <v>1</v>
+      </c>
+      <c r="V238">
+        <v>1</v>
+      </c>
+      <c r="X238">
+        <v>1</v>
+      </c>
+      <c r="AD238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:30">
       <c r="A239">
         <v>238</v>
       </c>
@@ -9325,8 +13008,26 @@
       <c r="E239" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="F239">
+        <v>69</v>
+      </c>
+      <c r="G239">
+        <v>5</v>
+      </c>
+      <c r="I239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="T239">
+        <v>1</v>
+      </c>
+      <c r="AD239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:30">
       <c r="A240">
         <v>239</v>
       </c>
@@ -9343,7 +13044,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:30">
       <c r="A241">
         <v>240</v>
       </c>
@@ -9359,8 +13060,29 @@
       <c r="E241" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="F241">
+        <v>56</v>
+      </c>
+      <c r="G241">
+        <v>10</v>
+      </c>
+      <c r="H241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="P241">
+        <v>1</v>
+      </c>
+      <c r="W241">
+        <v>1</v>
+      </c>
+      <c r="Z241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:30">
       <c r="A242">
         <v>241</v>
       </c>
@@ -9375,6 +13097,21 @@
       </c>
       <c r="E242" t="s">
         <v>372</v>
+      </c>
+      <c r="F242">
+        <v>61</v>
+      </c>
+      <c r="G242">
+        <v>4</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="T242">
+        <v>1</v>
+      </c>
+      <c r="AD242">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_shichigawahama_w4.xlsx
+++ b/data/data_shichigawahama_w4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45CFA08-47D9-4EE7-86ED-F032BE3B8FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C937BE-80BC-474A-87F2-3032172704E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$237</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="534">
   <si>
     <t>id</t>
   </si>
@@ -542,34 +542,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>七ヶ浜町吉田浜字野山五－九仮設八－八</t>
-    <rPh sb="4" eb="6">
-      <t>ヨシダ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヤマ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>カセツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ハチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>宍戸智</t>
     <rPh sb="2" eb="3">
       <t>シシド　サトシ</t>
@@ -3042,9 +3014,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>齋藤清市</t>
-  </si>
-  <si>
     <t>七ヶ浜町菖蒲田浜字宅地七二</t>
     <rPh sb="11" eb="12">
       <t>シチ</t>
@@ -3056,19 +3025,6 @@
   </si>
   <si>
     <t>松野兵次郎</t>
-  </si>
-  <si>
-    <t>七ヶ浜町湊浜字熊野四八-一</t>
-    <rPh sb="9" eb="10">
-      <t>ヨン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ハチ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>イチ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <t>佐藤正夫　</t>
@@ -3371,13 +3327,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>鈴木富子</t>
-    <rPh sb="0" eb="2">
-      <t>スズキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>鈴木政子</t>
     <rPh sb="0" eb="2">
       <t>スズキ</t>
@@ -3527,35 +3476,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>佐藤武志</t>
-    <rPh sb="0" eb="2">
-      <t>サトウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>タケシ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ココロザ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>七ヶ浜町東宮浜字東兼田二-五</t>
-    <rPh sb="9" eb="10">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ニ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ゴ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>伊藤兵四郎</t>
     <rPh sb="0" eb="2">
       <t>イトウ</t>
@@ -4531,9 +4451,6 @@
     <t>district_w4</t>
   </si>
   <si>
-    <t>name_w4</t>
-  </si>
-  <si>
     <t>address_w4</t>
   </si>
   <si>
@@ -5154,6 +5071,14 @@
   </si>
   <si>
     <t>v38_future_farm_operator_ja_corporate_farming</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>齋藤清市</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>name_w4</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -5210,18 +5135,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -5236,9 +5155,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -5520,7 +5438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD242"/>
+  <dimension ref="A1:AD237"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -5554,94 +5472,94 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>375</v>
+        <v>533</v>
       </c>
       <c r="D1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="F1" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="G1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="H1" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="I1" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="J1" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="K1" t="s">
+        <v>512</v>
+      </c>
+      <c r="L1" t="s">
+        <v>513</v>
+      </c>
+      <c r="M1" t="s">
+        <v>514</v>
+      </c>
+      <c r="N1" t="s">
+        <v>515</v>
+      </c>
+      <c r="O1" t="s">
+        <v>516</v>
+      </c>
+      <c r="P1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>518</v>
+      </c>
+      <c r="R1" t="s">
         <v>519</v>
       </c>
-      <c r="L1" t="s">
+      <c r="S1" t="s">
         <v>520</v>
       </c>
-      <c r="M1" t="s">
+      <c r="T1" t="s">
         <v>521</v>
       </c>
-      <c r="N1" t="s">
+      <c r="U1" t="s">
         <v>522</v>
       </c>
-      <c r="O1" t="s">
+      <c r="V1" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
         <v>524</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="X1" t="s">
         <v>525</v>
       </c>
-      <c r="R1" t="s">
+      <c r="Y1" t="s">
         <v>526</v>
       </c>
-      <c r="S1" t="s">
+      <c r="Z1" t="s">
         <v>527</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AA1" t="s">
         <v>528</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AB1" t="s">
         <v>529</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="AC1" t="s">
         <v>530</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AD1" t="s">
         <v>531</v>
-      </c>
-      <c r="X1" t="s">
-        <v>532</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>533</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>534</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>535</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>536</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>537</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -5652,7 +5570,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -5693,7 +5611,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="D3" t="s">
         <v>1</v>
@@ -5734,7 +5652,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D4" t="s">
         <v>1</v>
@@ -5772,7 +5690,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
@@ -5807,7 +5725,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -5839,7 +5757,7 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -5877,7 +5795,7 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -5909,7 +5827,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -5944,7 +5862,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -5965,10 +5883,10 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="O10" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="T10">
         <v>1</v>
@@ -5985,7 +5903,7 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -6023,7 +5941,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -6055,7 +5973,7 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -6081,7 +5999,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -6105,7 +6023,7 @@
         <v>6</v>
       </c>
       <c r="O14" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="Y14">
         <v>1</v>
@@ -6122,7 +6040,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -6139,7 +6057,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -6174,7 +6092,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -6206,7 +6124,7 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -6244,7 +6162,7 @@
         <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
@@ -6261,7 +6179,7 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -6293,7 +6211,7 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -6331,7 +6249,7 @@
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -6348,7 +6266,7 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -6383,7 +6301,7 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -6418,7 +6336,7 @@
         <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -6439,7 +6357,7 @@
         <v>6</v>
       </c>
       <c r="O25" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="T25">
         <v>1</v>
@@ -6459,7 +6377,7 @@
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
@@ -6476,7 +6394,7 @@
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="D27" t="s">
         <v>6</v>
@@ -6528,7 +6446,7 @@
         <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -6566,7 +6484,7 @@
         <v>36</v>
       </c>
       <c r="C30" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
@@ -6604,7 +6522,7 @@
         <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -6639,7 +6557,7 @@
         <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D32" t="s">
         <v>6</v>
@@ -6674,7 +6592,7 @@
         <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -6712,7 +6630,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="D34" t="s">
         <v>6</v>
@@ -6750,7 +6668,7 @@
         <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="D35" t="s">
         <v>6</v>
@@ -6788,7 +6706,7 @@
         <v>48</v>
       </c>
       <c r="C36" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D36" t="s">
         <v>6</v>
@@ -6809,10 +6727,10 @@
         <v>1</v>
       </c>
       <c r="N36" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="O36" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="U36">
         <v>1</v>
@@ -6832,7 +6750,7 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D37" t="s">
         <v>39</v>
@@ -6867,7 +6785,7 @@
         <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D38" t="s">
         <v>39</v>
@@ -6902,7 +6820,7 @@
         <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D39" t="s">
         <v>39</v>
@@ -6928,30 +6846,48 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="C40" t="s">
-        <v>275</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
         <v>39</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="F40">
+        <v>53</v>
+      </c>
+      <c r="G40">
+        <v>5</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:30">
       <c r="A41">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41">
-        <v>235</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>406</v>
       </c>
       <c r="D41" t="s">
         <v>39</v>
@@ -6960,33 +6896,24 @@
         <v>45</v>
       </c>
       <c r="F41">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="G41">
-        <v>5</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-      <c r="L41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T41">
-        <v>1</v>
-      </c>
-      <c r="X41">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:30">
       <c r="A42">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D42" t="s">
         <v>39</v>
@@ -6995,24 +6922,39 @@
         <v>46</v>
       </c>
       <c r="F42">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
       </c>
       <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="AB42">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:30">
       <c r="A43">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D43" t="s">
         <v>39</v>
@@ -7021,12 +6963,12 @@
         <v>47</v>
       </c>
       <c r="F43">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G43">
-        <v>4</v>
-      </c>
-      <c r="J43">
+        <v>3</v>
+      </c>
+      <c r="I43">
         <v>1</v>
       </c>
       <c r="L43">
@@ -7035,25 +6977,19 @@
       <c r="T43">
         <v>1</v>
       </c>
-      <c r="V43">
-        <v>1</v>
-      </c>
-      <c r="X43">
-        <v>1</v>
-      </c>
-      <c r="AB43">
+      <c r="AD43">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:30">
       <c r="A44">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C44" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
@@ -7062,7 +6998,7 @@
         <v>48</v>
       </c>
       <c r="F44">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G44">
         <v>3</v>
@@ -7070,10 +7006,10 @@
       <c r="I44">
         <v>1</v>
       </c>
-      <c r="L44">
-        <v>1</v>
-      </c>
-      <c r="T44">
+      <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="U44">
         <v>1</v>
       </c>
       <c r="AD44">
@@ -7082,13 +7018,13 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D45" t="s">
         <v>39</v>
@@ -7097,18 +7033,21 @@
         <v>49</v>
       </c>
       <c r="F45">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45">
         <v>1</v>
       </c>
-      <c r="M45">
+      <c r="L45">
         <v>1</v>
       </c>
       <c r="U45">
+        <v>1</v>
+      </c>
+      <c r="X45">
         <v>1</v>
       </c>
       <c r="AD45">
@@ -7117,13 +7056,13 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46">
-        <v>64</v>
+        <v>238</v>
       </c>
       <c r="C46" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D46" t="s">
         <v>39</v>
@@ -7132,7 +7071,7 @@
         <v>50</v>
       </c>
       <c r="F46">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -7143,25 +7082,25 @@
       <c r="L46">
         <v>1</v>
       </c>
-      <c r="U46">
+      <c r="T46">
         <v>1</v>
       </c>
       <c r="X46">
         <v>1</v>
       </c>
-      <c r="AD46">
+      <c r="AB46">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:30">
       <c r="A47">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47">
-        <v>238</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D47" t="s">
         <v>39</v>
@@ -7169,37 +7108,16 @@
       <c r="E47" t="s">
         <v>51</v>
       </c>
-      <c r="F47">
-        <v>78</v>
-      </c>
-      <c r="G47">
-        <v>2</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-      <c r="L47">
-        <v>1</v>
-      </c>
-      <c r="T47">
-        <v>1</v>
-      </c>
-      <c r="X47">
-        <v>1</v>
-      </c>
-      <c r="AB47">
-        <v>1</v>
-      </c>
     </row>
     <row r="48" spans="1:30">
       <c r="A48">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
         <v>39</v>
@@ -7207,16 +7125,31 @@
       <c r="E48" t="s">
         <v>52</v>
       </c>
+      <c r="F48">
+        <v>49</v>
+      </c>
+      <c r="G48">
+        <v>6</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="T48">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:30">
       <c r="A49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D49" t="s">
         <v>39</v>
@@ -7225,12 +7158,12 @@
         <v>53</v>
       </c>
       <c r="F49">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G49">
-        <v>6</v>
-      </c>
-      <c r="J49">
+        <v>2</v>
+      </c>
+      <c r="I49">
         <v>1</v>
       </c>
       <c r="L49">
@@ -7242,13 +7175,13 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D50" t="s">
         <v>39</v>
@@ -7257,10 +7190,10 @@
         <v>54</v>
       </c>
       <c r="F50">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -7269,18 +7202,21 @@
         <v>1</v>
       </c>
       <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="AD50">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:30">
       <c r="A51">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D51" t="s">
         <v>39</v>
@@ -7288,34 +7224,16 @@
       <c r="E51" t="s">
         <v>55</v>
       </c>
-      <c r="F51">
-        <v>83</v>
-      </c>
-      <c r="G51">
-        <v>3</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="L51">
-        <v>1</v>
-      </c>
-      <c r="T51">
-        <v>1</v>
-      </c>
-      <c r="AD51">
-        <v>1</v>
-      </c>
     </row>
     <row r="52" spans="1:30">
       <c r="A52">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D52" t="s">
         <v>39</v>
@@ -7326,13 +7244,13 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D53" t="s">
         <v>39</v>
@@ -7340,16 +7258,31 @@
       <c r="E53" t="s">
         <v>57</v>
       </c>
+      <c r="F53">
+        <v>62</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="L53">
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="AD53">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:30">
       <c r="A54">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D54" t="s">
         <v>39</v>
@@ -7358,7 +7291,10 @@
         <v>58</v>
       </c>
       <c r="F54">
-        <v>62</v>
+        <v>78</v>
+      </c>
+      <c r="G54" t="s">
+        <v>493</v>
       </c>
       <c r="I54">
         <v>1</v>
@@ -7366,22 +7302,19 @@
       <c r="L54">
         <v>1</v>
       </c>
-      <c r="T54">
-        <v>1</v>
-      </c>
-      <c r="AD54">
+      <c r="S54">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:30">
       <c r="A55">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D55" t="s">
         <v>39</v>
@@ -7392,8 +7325,8 @@
       <c r="F55">
         <v>78</v>
       </c>
-      <c r="G55" t="s">
-        <v>500</v>
+      <c r="G55">
+        <v>2</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -7402,56 +7335,62 @@
         <v>1</v>
       </c>
       <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="X55">
+        <v>1</v>
+      </c>
+      <c r="AD55">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:30">
       <c r="A56">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="C56" t="s">
-        <v>427</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
         <v>39</v>
       </c>
       <c r="E56" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F56">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>1</v>
       </c>
       <c r="L56">
         <v>1</v>
       </c>
-      <c r="S56">
-        <v>1</v>
-      </c>
-      <c r="X56">
-        <v>1</v>
-      </c>
-      <c r="AD56">
+      <c r="Q56">
+        <v>1</v>
+      </c>
+      <c r="Y56">
+        <v>1</v>
+      </c>
+      <c r="AA56">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:30">
       <c r="A57">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57">
-        <v>250</v>
+        <v>81</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>421</v>
       </c>
       <c r="D57" t="s">
         <v>39</v>
@@ -7460,36 +7399,36 @@
         <v>62</v>
       </c>
       <c r="F57">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
-      </c>
-      <c r="L57">
+        <v>8</v>
+      </c>
+      <c r="I57">
         <v>1</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
-      <c r="Y57">
-        <v>1</v>
-      </c>
-      <c r="AA57">
+      <c r="V57">
+        <v>1</v>
+      </c>
+      <c r="X57">
+        <v>1</v>
+      </c>
+      <c r="AB57">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:30">
       <c r="A58">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D58" t="s">
         <v>39</v>
@@ -7498,15 +7437,15 @@
         <v>63</v>
       </c>
       <c r="F58">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G58">
-        <v>8</v>
-      </c>
-      <c r="I58">
-        <v>1</v>
-      </c>
-      <c r="Q58">
+        <v>7</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="L58">
         <v>1</v>
       </c>
       <c r="V58">
@@ -7521,13 +7460,13 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D59" t="s">
         <v>39</v>
@@ -7536,276 +7475,297 @@
         <v>64</v>
       </c>
       <c r="F59">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G59">
-        <v>7</v>
-      </c>
-      <c r="J59">
+        <v>2</v>
+      </c>
+      <c r="I59">
         <v>1</v>
       </c>
       <c r="L59">
         <v>1</v>
       </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
       <c r="V59">
         <v>1</v>
       </c>
       <c r="X59">
         <v>1</v>
       </c>
-      <c r="AB59">
+      <c r="AD59">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:30">
       <c r="A60">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D60" t="s">
         <v>39</v>
       </c>
       <c r="E60" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F60">
-        <v>72</v>
-      </c>
-      <c r="G60">
-        <v>2</v>
-      </c>
-      <c r="I60">
+        <v>55</v>
+      </c>
+      <c r="H60">
         <v>1</v>
       </c>
       <c r="L60">
         <v>1</v>
       </c>
-      <c r="T60">
-        <v>1</v>
-      </c>
-      <c r="V60">
-        <v>1</v>
-      </c>
-      <c r="X60">
-        <v>1</v>
-      </c>
-      <c r="AD60">
+      <c r="AB60">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:30">
       <c r="A61">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="D61" t="s">
         <v>39</v>
       </c>
       <c r="E61" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="F61">
+        <v>65</v>
+      </c>
+      <c r="G61">
+        <v>3</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+      <c r="Q61">
+        <v>1</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="X61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:30">
       <c r="A62">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C62" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D62" t="s">
         <v>39</v>
       </c>
       <c r="E62" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F62">
-        <v>55</v>
-      </c>
-      <c r="H62">
+        <v>74</v>
+      </c>
+      <c r="J62">
         <v>1</v>
       </c>
       <c r="L62">
         <v>1</v>
       </c>
-      <c r="AB62">
+      <c r="T62">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:30">
       <c r="A63">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D63" t="s">
         <v>39</v>
       </c>
       <c r="E63" t="s">
-        <v>68</v>
-      </c>
-      <c r="F63">
-        <v>65</v>
-      </c>
-      <c r="G63">
-        <v>3</v>
-      </c>
-      <c r="I63">
-        <v>1</v>
-      </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-      <c r="Q63">
-        <v>1</v>
-      </c>
-      <c r="V63">
-        <v>1</v>
-      </c>
-      <c r="X63">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:30">
       <c r="A64">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B64">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D64" t="s">
         <v>39</v>
       </c>
       <c r="E64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F64">
-        <v>74</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
-      </c>
-      <c r="L64">
-        <v>1</v>
-      </c>
-      <c r="T64">
+        <v>89</v>
+      </c>
+      <c r="G64">
+        <v>7</v>
+      </c>
+      <c r="I64">
+        <v>1</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+      <c r="N64" t="s">
+        <v>500</v>
+      </c>
+      <c r="O64" t="s">
+        <v>501</v>
+      </c>
+      <c r="S64">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:30">
       <c r="A65">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C65" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D65" t="s">
         <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:30">
       <c r="A66">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B66">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C66" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D66" t="s">
         <v>39</v>
       </c>
       <c r="E66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F66">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="G66">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I66">
         <v>1</v>
       </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="N66" t="s">
-        <v>507</v>
-      </c>
-      <c r="O66" t="s">
-        <v>508</v>
-      </c>
-      <c r="S66">
+      <c r="L66">
+        <v>1</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+      <c r="X66">
+        <v>1</v>
+      </c>
+      <c r="AC66">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:30">
       <c r="A67">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D67" t="s">
         <v>39</v>
       </c>
       <c r="E67" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="G67">
+        <v>6</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <v>1</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>1</v>
+      </c>
+      <c r="Z67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:30">
       <c r="A68">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C68" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D68" t="s">
         <v>39</v>
       </c>
       <c r="E68" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F68">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G68">
         <v>3</v>
       </c>
-      <c r="I68">
+      <c r="J68">
         <v>1</v>
       </c>
       <c r="L68">
@@ -7823,516 +7783,495 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B69">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D69" t="s">
         <v>39</v>
       </c>
       <c r="E69" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="F69">
+        <v>76</v>
       </c>
       <c r="G69">
-        <v>6</v>
-      </c>
-      <c r="H69">
-        <v>1</v>
-      </c>
-      <c r="M69">
-        <v>1</v>
-      </c>
-      <c r="Q69">
-        <v>1</v>
-      </c>
-      <c r="W69">
-        <v>1</v>
-      </c>
-      <c r="Y69">
-        <v>1</v>
-      </c>
-      <c r="Z69">
+        <v>5</v>
+      </c>
+      <c r="I69">
+        <v>1</v>
+      </c>
+      <c r="L69">
+        <v>1</v>
+      </c>
+      <c r="S69">
+        <v>1</v>
+      </c>
+      <c r="AC69">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:30">
       <c r="A70">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D70" t="s">
         <v>39</v>
       </c>
       <c r="E70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F70">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G70">
-        <v>3</v>
-      </c>
-      <c r="J70">
-        <v>1</v>
-      </c>
-      <c r="L70">
-        <v>1</v>
-      </c>
-      <c r="T70">
-        <v>1</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="AC70">
+        <v>6</v>
+      </c>
+      <c r="H70">
+        <v>1</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+      <c r="P70">
+        <v>1</v>
+      </c>
+      <c r="W70">
+        <v>1</v>
+      </c>
+      <c r="AD70">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:30">
       <c r="A71">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C71" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D71" t="s">
         <v>39</v>
       </c>
       <c r="E71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F71">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G71">
-        <v>5</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="S71">
-        <v>1</v>
-      </c>
-      <c r="AC71">
+        <v>7</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="W71">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:30">
       <c r="A72">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B72">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D72" t="s">
         <v>39</v>
       </c>
       <c r="E72" t="s">
-        <v>77</v>
-      </c>
-      <c r="F72">
-        <v>54</v>
-      </c>
-      <c r="G72">
-        <v>6</v>
-      </c>
-      <c r="H72">
-        <v>1</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
-      </c>
-      <c r="P72">
-        <v>1</v>
-      </c>
-      <c r="W72">
-        <v>1</v>
-      </c>
-      <c r="AD72">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:30">
       <c r="A73">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73">
-        <v>86</v>
+        <v>270</v>
       </c>
       <c r="C73" t="s">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="D73" t="s">
         <v>39</v>
       </c>
       <c r="E73" t="s">
-        <v>78</v>
-      </c>
-      <c r="F73">
-        <v>79</v>
-      </c>
-      <c r="G73">
-        <v>7</v>
-      </c>
-      <c r="H73">
-        <v>1</v>
-      </c>
-      <c r="K73">
-        <v>1</v>
-      </c>
-      <c r="R73">
-        <v>1</v>
-      </c>
-      <c r="W73">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:30">
       <c r="A74">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C74" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D74" t="s">
         <v>39</v>
       </c>
       <c r="E74" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75" spans="1:30">
       <c r="A75">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>438</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F75">
+        <v>63</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="K75">
+        <v>1</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="W75">
+        <v>1</v>
+      </c>
+      <c r="AD75">
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:30">
       <c r="A76">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C76" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="E76" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="F76">
+        <v>73</v>
+      </c>
+      <c r="G76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>1</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="AD76">
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:30">
       <c r="A77">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C77" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77" t="s">
-        <v>84</v>
-      </c>
-      <c r="F77">
-        <v>63</v>
-      </c>
-      <c r="H77">
-        <v>1</v>
-      </c>
-      <c r="K77">
-        <v>1</v>
-      </c>
-      <c r="R77">
-        <v>1</v>
-      </c>
-      <c r="W77">
-        <v>1</v>
-      </c>
-      <c r="AD77">
-        <v>1</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:30">
       <c r="A78">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B78">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F78">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G78">
-        <v>3</v>
-      </c>
-      <c r="I78">
+        <v>7</v>
+      </c>
+      <c r="H78">
         <v>1</v>
       </c>
       <c r="L78">
         <v>1</v>
       </c>
-      <c r="T78">
-        <v>1</v>
-      </c>
-      <c r="AD78">
+      <c r="N78" t="s">
+        <v>502</v>
+      </c>
+      <c r="O78" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:30">
       <c r="A79">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B79">
-        <v>102</v>
+        <v>257</v>
       </c>
       <c r="C79" t="s">
-        <v>447</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>86</v>
+        <v>88</v>
+      </c>
+      <c r="F79">
+        <v>51</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="V79">
+        <v>1</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="AD79">
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:30">
       <c r="A80">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B80">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C80" t="s">
-        <v>448</v>
+        <v>89</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E80" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F80">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G80">
-        <v>7</v>
-      </c>
-      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
         <v>1</v>
       </c>
       <c r="L80">
         <v>1</v>
       </c>
-      <c r="N80" t="s">
-        <v>509</v>
-      </c>
-      <c r="O80" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q80">
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="AB80">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:30">
       <c r="A81">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B81">
-        <v>257</v>
+        <v>112</v>
       </c>
       <c r="C81" t="s">
-        <v>88</v>
+        <v>442</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E81" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81">
-        <v>51</v>
-      </c>
-      <c r="G81">
-        <v>2</v>
-      </c>
-      <c r="I81">
-        <v>1</v>
-      </c>
-      <c r="L81">
-        <v>1</v>
-      </c>
-      <c r="T81">
-        <v>1</v>
-      </c>
-      <c r="V81">
-        <v>1</v>
-      </c>
-      <c r="X81">
-        <v>1</v>
-      </c>
-      <c r="AD81">
-        <v>1</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="1:30">
       <c r="A82">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>443</v>
       </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F82">
-        <v>69</v>
-      </c>
-      <c r="G82">
-        <v>2</v>
-      </c>
-      <c r="I82">
+        <v>80</v>
+      </c>
+      <c r="J82">
         <v>1</v>
       </c>
       <c r="L82">
         <v>1</v>
       </c>
+      <c r="N82" t="s">
+        <v>502</v>
+      </c>
+      <c r="O82" t="s">
+        <v>503</v>
+      </c>
       <c r="T82">
         <v>1</v>
       </c>
-      <c r="AB82">
+      <c r="X82">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:30">
       <c r="A83">
+        <v>84</v>
+      </c>
+      <c r="B83">
+        <v>116</v>
+      </c>
+      <c r="C83" t="s">
+        <v>444</v>
+      </c>
+      <c r="D83" t="s">
         <v>82</v>
       </c>
-      <c r="B83">
-        <v>112</v>
-      </c>
-      <c r="C83" t="s">
-        <v>449</v>
-      </c>
-      <c r="D83" t="s">
-        <v>83</v>
-      </c>
       <c r="E83" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="F83">
+        <v>61</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+      <c r="AC83">
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:30">
       <c r="A84">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B84">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C84" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="D84" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
-        <v>93</v>
-      </c>
-      <c r="F84">
-        <v>80</v>
-      </c>
-      <c r="J84">
-        <v>1</v>
-      </c>
-      <c r="L84">
-        <v>1</v>
-      </c>
-      <c r="N84" t="s">
-        <v>509</v>
-      </c>
-      <c r="O84" t="s">
-        <v>510</v>
-      </c>
-      <c r="T84">
-        <v>1</v>
-      </c>
-      <c r="X84">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="1:30">
       <c r="A85">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B85">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C85" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F85">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G85">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -8340,51 +8279,75 @@
       <c r="L85">
         <v>1</v>
       </c>
-      <c r="S85">
-        <v>1</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="AC85">
+      <c r="Q85">
+        <v>1</v>
+      </c>
+      <c r="V85">
+        <v>1</v>
+      </c>
+      <c r="AB85">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:30">
       <c r="A86">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B86">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C86" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E86" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="F86">
+        <v>65</v>
+      </c>
+      <c r="G86">
+        <v>7</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="N86" t="s">
+        <v>502</v>
+      </c>
+      <c r="O86" t="s">
+        <v>504</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="AD86">
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:30">
       <c r="A87">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B87">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C87" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E87" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F87">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G87">
         <v>7</v>
@@ -8395,10 +8358,10 @@
       <c r="L87">
         <v>1</v>
       </c>
-      <c r="Q87">
-        <v>1</v>
-      </c>
-      <c r="V87">
+      <c r="S87">
+        <v>1</v>
+      </c>
+      <c r="X87">
         <v>1</v>
       </c>
       <c r="AB87">
@@ -8407,392 +8370,380 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B88">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C88" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E88" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F88">
         <v>65</v>
       </c>
       <c r="G88">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J88">
         <v>1</v>
       </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="N88" t="s">
-        <v>509</v>
-      </c>
-      <c r="O88" t="s">
-        <v>511</v>
-      </c>
-      <c r="T88">
-        <v>1</v>
-      </c>
-      <c r="AD88">
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="V88">
+        <v>1</v>
+      </c>
+      <c r="AC88">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:30">
       <c r="A89">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B89">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C89" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E89" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F89">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G89">
-        <v>7</v>
-      </c>
-      <c r="I89">
+        <v>5</v>
+      </c>
+      <c r="J89">
         <v>1</v>
       </c>
       <c r="L89">
         <v>1</v>
       </c>
-      <c r="S89">
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="V89">
         <v>1</v>
       </c>
       <c r="X89">
         <v>1</v>
       </c>
-      <c r="AB89">
+      <c r="Z89">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:30">
       <c r="A90">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B90">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E90" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F90">
         <v>65</v>
       </c>
       <c r="G90">
-        <v>5</v>
-      </c>
-      <c r="J90">
-        <v>1</v>
-      </c>
-      <c r="K90">
-        <v>1</v>
-      </c>
-      <c r="P90">
-        <v>1</v>
-      </c>
-      <c r="V90">
-        <v>1</v>
-      </c>
-      <c r="AC90">
+        <v>7</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="T90">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:30">
       <c r="A91">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B91">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C91" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="D91" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F91">
-        <v>65</v>
-      </c>
-      <c r="G91">
-        <v>5</v>
-      </c>
-      <c r="J91">
+        <v>63</v>
+      </c>
+      <c r="I91">
         <v>1</v>
       </c>
       <c r="L91">
         <v>1</v>
       </c>
-      <c r="Q91">
-        <v>1</v>
-      </c>
       <c r="V91">
-        <v>1</v>
-      </c>
-      <c r="X91">
-        <v>1</v>
-      </c>
-      <c r="Z91">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:30">
       <c r="A92">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B92">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E92" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F92">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G92">
-        <v>7</v>
-      </c>
-      <c r="I92">
-        <v>1</v>
-      </c>
-      <c r="L92">
-        <v>1</v>
-      </c>
-      <c r="T92">
+        <v>4</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>1</v>
+      </c>
+      <c r="V92">
+        <v>1</v>
+      </c>
+      <c r="AC92">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:30">
       <c r="A93">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B93">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E93" t="s">
-        <v>102</v>
-      </c>
-      <c r="F93">
-        <v>63</v>
-      </c>
-      <c r="I93">
-        <v>1</v>
-      </c>
-      <c r="L93">
-        <v>1</v>
-      </c>
-      <c r="V93">
-        <v>1</v>
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:30">
       <c r="A94">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B94">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C94" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="D94" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E94" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F94">
-        <v>55</v>
-      </c>
-      <c r="G94">
-        <v>4</v>
-      </c>
-      <c r="J94">
-        <v>1</v>
-      </c>
-      <c r="K94">
-        <v>1</v>
-      </c>
-      <c r="V94">
-        <v>1</v>
-      </c>
-      <c r="AC94">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94" t="s">
+        <v>505</v>
+      </c>
+      <c r="O94" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:30">
       <c r="A95">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B95">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="C95" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E95" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="F95">
+        <v>65</v>
+      </c>
+      <c r="G95">
+        <v>4</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="V95">
+        <v>1</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="AB95">
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:30">
       <c r="A96">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B96">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="E96" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F96">
-        <v>70</v>
-      </c>
-      <c r="M96">
-        <v>1</v>
-      </c>
-      <c r="N96" t="s">
-        <v>512</v>
-      </c>
-      <c r="O96" t="s">
-        <v>513</v>
+        <v>47</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="L96">
+        <v>1</v>
+      </c>
+      <c r="T96">
+        <v>1</v>
+      </c>
+      <c r="AC96">
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:30">
       <c r="A97">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B97">
-        <v>271</v>
+        <v>130</v>
       </c>
       <c r="C97" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="D97" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="E97" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F97">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I97">
         <v>1</v>
       </c>
-      <c r="Q97">
-        <v>1</v>
-      </c>
-      <c r="V97">
-        <v>1</v>
-      </c>
-      <c r="X97">
-        <v>1</v>
-      </c>
-      <c r="AB97">
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="T97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:30">
       <c r="A98">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B98">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C98" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E98" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F98">
-        <v>47</v>
-      </c>
-      <c r="I98">
+        <v>31</v>
+      </c>
+      <c r="G98">
+        <v>7</v>
+      </c>
+      <c r="J98">
         <v>1</v>
       </c>
       <c r="L98">
         <v>1</v>
       </c>
-      <c r="T98">
-        <v>1</v>
-      </c>
-      <c r="AC98">
+      <c r="S98">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:30">
       <c r="A99">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B99">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C99" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D99" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E99" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F99">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G99">
         <v>5</v>
@@ -8806,161 +8757,149 @@
       <c r="T99">
         <v>1</v>
       </c>
-      <c r="AD99">
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="AC99">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:30">
       <c r="A100">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B100">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C100" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E100" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F100">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G100">
-        <v>7</v>
-      </c>
-      <c r="J100">
+        <v>5</v>
+      </c>
+      <c r="I100">
         <v>1</v>
       </c>
       <c r="L100">
         <v>1</v>
       </c>
-      <c r="S100">
+      <c r="T100">
+        <v>1</v>
+      </c>
+      <c r="X100">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:30">
       <c r="A101">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B101">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E101" t="s">
-        <v>111</v>
-      </c>
-      <c r="F101">
-        <v>45</v>
-      </c>
-      <c r="G101">
-        <v>5</v>
-      </c>
-      <c r="I101">
-        <v>1</v>
-      </c>
-      <c r="L101">
-        <v>1</v>
-      </c>
-      <c r="T101">
-        <v>1</v>
-      </c>
-      <c r="X101">
-        <v>1</v>
-      </c>
-      <c r="AC101">
-        <v>1</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102" spans="1:30">
       <c r="A102">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B102">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C102" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F102">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I102">
         <v>1</v>
       </c>
-      <c r="L102">
+      <c r="K102">
         <v>1</v>
       </c>
       <c r="T102">
         <v>1</v>
       </c>
-      <c r="X102">
+      <c r="AD102">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:30">
       <c r="A103">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B103">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" spans="1:30">
       <c r="A104">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B104">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C104" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="D104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E104" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F104">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I104">
         <v>1</v>
       </c>
-      <c r="K104">
+      <c r="L104">
         <v>1</v>
       </c>
       <c r="T104">
+        <v>3</v>
+      </c>
+      <c r="X104">
         <v>1</v>
       </c>
       <c r="AD104">
@@ -8969,51 +8908,57 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B105">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C105" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="D105" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E105" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:30">
       <c r="A106">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B106">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C106" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="D106" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F106">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G106">
-        <v>7</v>
-      </c>
-      <c r="I106">
-        <v>1</v>
-      </c>
-      <c r="L106">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106" t="s">
+        <v>505</v>
+      </c>
+      <c r="O106" t="s">
+        <v>506</v>
       </c>
       <c r="T106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X106">
         <v>1</v>
@@ -9024,54 +8969,66 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107">
+        <v>108</v>
+      </c>
+      <c r="B107">
+        <v>141</v>
+      </c>
+      <c r="C107" t="s">
+        <v>468</v>
+      </c>
+      <c r="D107" t="s">
         <v>106</v>
       </c>
-      <c r="B107">
-        <v>140</v>
-      </c>
-      <c r="C107" t="s">
-        <v>473</v>
-      </c>
-      <c r="D107" t="s">
-        <v>107</v>
-      </c>
       <c r="E107" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="F107">
+        <v>70</v>
+      </c>
+      <c r="G107">
+        <v>2</v>
+      </c>
+      <c r="I107">
+        <v>1</v>
+      </c>
+      <c r="L107">
+        <v>1</v>
+      </c>
+      <c r="T107">
+        <v>1</v>
+      </c>
+      <c r="AD107">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:30">
       <c r="A108">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B108">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C108" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E108" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F108">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G108">
-        <v>6</v>
-      </c>
-      <c r="J108">
-        <v>1</v>
-      </c>
-      <c r="M108">
-        <v>1</v>
-      </c>
-      <c r="N108" t="s">
-        <v>512</v>
-      </c>
-      <c r="O108" t="s">
-        <v>513</v>
+        <v>7</v>
+      </c>
+      <c r="I108">
+        <v>1</v>
+      </c>
+      <c r="L108">
+        <v>1</v>
       </c>
       <c r="T108">
         <v>1</v>
@@ -9085,57 +9042,54 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B109">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C109" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E109" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F109">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G109">
-        <v>2</v>
-      </c>
-      <c r="I109">
-        <v>1</v>
-      </c>
-      <c r="L109">
-        <v>1</v>
-      </c>
-      <c r="T109">
-        <v>1</v>
-      </c>
-      <c r="AD109">
+        <v>4</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+      <c r="P109">
+        <v>1</v>
+      </c>
+      <c r="V109">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:30">
       <c r="A110">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B110">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="D110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E110" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F110">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G110">
         <v>7</v>
@@ -9146,69 +9100,69 @@
       <c r="L110">
         <v>1</v>
       </c>
-      <c r="T110">
+      <c r="U110">
         <v>1</v>
       </c>
       <c r="X110">
         <v>1</v>
       </c>
-      <c r="AD110">
+      <c r="AC110">
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:30">
       <c r="A111">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B111">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C111" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D111" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E111" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F111">
-        <v>61</v>
-      </c>
-      <c r="G111">
-        <v>4</v>
-      </c>
-      <c r="K111">
-        <v>1</v>
-      </c>
-      <c r="P111">
-        <v>1</v>
-      </c>
-      <c r="V111">
+        <v>74</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="T111">
+        <v>1</v>
+      </c>
+      <c r="X111">
+        <v>1</v>
+      </c>
+      <c r="AD111">
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:30">
       <c r="A112">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B112">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="C112" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E112" t="s">
-        <v>122</v>
-      </c>
-      <c r="F112">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="G112">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I112">
         <v>1</v>
@@ -9217,6 +9171,9 @@
         <v>1</v>
       </c>
       <c r="U112">
+        <v>1</v>
+      </c>
+      <c r="V112">
         <v>1</v>
       </c>
       <c r="X112">
@@ -9228,22 +9185,22 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B113">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="D113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E113" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F113">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I113">
         <v>1</v>
@@ -9252,9 +9209,6 @@
         <v>1</v>
       </c>
       <c r="T113">
-        <v>1</v>
-      </c>
-      <c r="X113">
         <v>1</v>
       </c>
       <c r="AD113">
@@ -9263,103 +9217,85 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B114">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C114" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E114" t="s">
-        <v>124</v>
-      </c>
-      <c r="G114">
-        <v>3</v>
-      </c>
-      <c r="I114">
-        <v>1</v>
-      </c>
-      <c r="L114">
-        <v>1</v>
-      </c>
-      <c r="U114">
-        <v>1</v>
-      </c>
-      <c r="V114">
+        <v>125</v>
+      </c>
+      <c r="F114">
+        <v>67</v>
+      </c>
+      <c r="J114">
+        <v>1</v>
+      </c>
+      <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="Q114">
         <v>1</v>
       </c>
       <c r="X114">
         <v>1</v>
       </c>
-      <c r="AC114">
+      <c r="AD114">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:30">
       <c r="A115">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B115">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C115" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="D115" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E115" t="s">
-        <v>125</v>
-      </c>
-      <c r="F115">
-        <v>70</v>
-      </c>
-      <c r="I115">
-        <v>1</v>
-      </c>
-      <c r="L115">
-        <v>1</v>
-      </c>
-      <c r="T115">
-        <v>1</v>
-      </c>
-      <c r="AD115">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" spans="1:30">
       <c r="A116">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B116">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C116" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D116" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E116" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F116">
-        <v>67</v>
-      </c>
-      <c r="J116">
-        <v>1</v>
-      </c>
-      <c r="M116">
-        <v>1</v>
-      </c>
-      <c r="Q116">
-        <v>1</v>
-      </c>
-      <c r="X116">
+        <v>47</v>
+      </c>
+      <c r="G116">
+        <v>7</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>1</v>
+      </c>
+      <c r="T116">
         <v>1</v>
       </c>
       <c r="AD116">
@@ -9368,45 +9304,54 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B117">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="C117" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="D117" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E117" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="F117">
+        <v>38</v>
+      </c>
+      <c r="G117">
+        <v>5</v>
+      </c>
+      <c r="I117">
+        <v>1</v>
+      </c>
+      <c r="M117">
+        <v>1</v>
+      </c>
+      <c r="AB117">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:30">
       <c r="A118">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B118">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C118" t="s">
-        <v>484</v>
+        <v>129</v>
       </c>
       <c r="D118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E118" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F118">
-        <v>47</v>
-      </c>
-      <c r="G118">
-        <v>7</v>
-      </c>
-      <c r="I118">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="L118">
         <v>1</v>
@@ -9414,144 +9359,159 @@
       <c r="T118">
         <v>1</v>
       </c>
-      <c r="AD118">
+      <c r="X118">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:30">
       <c r="A119">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B119">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="C119" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E119" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F119">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I119">
         <v>1</v>
       </c>
-      <c r="M119">
-        <v>1</v>
-      </c>
-      <c r="AB119">
+      <c r="L119">
+        <v>1</v>
+      </c>
+      <c r="T119">
+        <v>1</v>
+      </c>
+      <c r="X119">
+        <v>1</v>
+      </c>
+      <c r="AD119">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:30">
       <c r="A120">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B120">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C120" t="s">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="D120" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E120" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F120">
-        <v>78</v>
+        <v>66</v>
+      </c>
+      <c r="G120">
+        <v>8</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
       </c>
       <c r="L120">
         <v>1</v>
       </c>
-      <c r="T120">
+      <c r="R120">
+        <v>1</v>
+      </c>
+      <c r="V120">
         <v>1</v>
       </c>
       <c r="X120">
+        <v>1</v>
+      </c>
+      <c r="AD120">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:30">
       <c r="A121">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B121">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C121" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D121" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E121" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F121">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G121">
-        <v>6</v>
-      </c>
-      <c r="I121">
-        <v>1</v>
-      </c>
-      <c r="L121">
+        <v>5</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="M121">
+        <v>1</v>
+      </c>
+      <c r="Q121">
         <v>1</v>
       </c>
       <c r="T121">
         <v>1</v>
       </c>
-      <c r="X121">
-        <v>1</v>
-      </c>
-      <c r="AD121">
+      <c r="Y121">
+        <v>1</v>
+      </c>
+      <c r="Z121">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:30">
       <c r="A122">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B122">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C122" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D122" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E122" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F122">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G122">
-        <v>8</v>
-      </c>
-      <c r="I122">
+        <v>7</v>
+      </c>
+      <c r="J122">
         <v>1</v>
       </c>
       <c r="L122">
         <v>1</v>
       </c>
-      <c r="R122">
-        <v>1</v>
-      </c>
-      <c r="V122">
-        <v>1</v>
-      </c>
-      <c r="X122">
+      <c r="T122">
         <v>1</v>
       </c>
       <c r="AD122">
@@ -9560,225 +9520,219 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B123">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C123" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D123" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E123" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F123">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="G123">
-        <v>5</v>
-      </c>
-      <c r="H123">
-        <v>1</v>
-      </c>
-      <c r="M123">
-        <v>1</v>
-      </c>
-      <c r="Q123">
-        <v>1</v>
-      </c>
-      <c r="T123">
-        <v>1</v>
-      </c>
-      <c r="Y123">
-        <v>1</v>
-      </c>
-      <c r="Z123">
+        <v>3</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="L123">
+        <v>1</v>
+      </c>
+      <c r="S123">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:30">
       <c r="A124">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B124">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C124" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D124" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E124" t="s">
-        <v>135</v>
-      </c>
-      <c r="F124">
-        <v>69</v>
-      </c>
-      <c r="G124">
-        <v>7</v>
-      </c>
-      <c r="J124">
-        <v>1</v>
-      </c>
-      <c r="L124">
-        <v>1</v>
-      </c>
-      <c r="T124">
-        <v>1</v>
-      </c>
-      <c r="AD124">
-        <v>1</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125" spans="1:30">
       <c r="A125">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B125">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C125" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D125" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E125" t="s">
-        <v>136</v>
-      </c>
-      <c r="F125">
-        <v>74</v>
-      </c>
-      <c r="G125">
-        <v>3</v>
-      </c>
-      <c r="I125">
-        <v>1</v>
-      </c>
-      <c r="L125">
-        <v>1</v>
-      </c>
-      <c r="S125">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" spans="1:30">
       <c r="A126">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B126">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C126" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D126" t="s">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="E126" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:30">
       <c r="A127">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B127">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C127" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="D127" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E127" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="F127">
+        <v>64</v>
+      </c>
+      <c r="G127">
+        <v>5</v>
+      </c>
+      <c r="I127">
+        <v>1</v>
+      </c>
+      <c r="K127">
+        <v>1</v>
+      </c>
+      <c r="Q127">
+        <v>1</v>
+      </c>
+      <c r="V127">
+        <v>1</v>
+      </c>
+      <c r="X127">
+        <v>1</v>
+      </c>
+      <c r="AC127">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:30">
       <c r="A128">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B128">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C128" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E128" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="F128">
+        <v>50</v>
+      </c>
+      <c r="G128">
+        <v>5</v>
+      </c>
+      <c r="I128">
+        <v>1</v>
+      </c>
+      <c r="L128">
+        <v>1</v>
+      </c>
+      <c r="AD128">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:30">
       <c r="A129">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B129">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C129" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D129" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E129" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F129">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G129">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I129">
         <v>1</v>
       </c>
-      <c r="K129">
-        <v>1</v>
-      </c>
-      <c r="Q129">
-        <v>1</v>
-      </c>
-      <c r="V129">
+      <c r="L129">
+        <v>1</v>
+      </c>
+      <c r="S129">
         <v>1</v>
       </c>
       <c r="X129">
         <v>1</v>
       </c>
-      <c r="AC129">
+      <c r="AA129">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:30">
       <c r="A130">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B130">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C130" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D130" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E130" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F130">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="G130">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -9786,71 +9740,71 @@
       <c r="L130">
         <v>1</v>
       </c>
-      <c r="AD130">
+      <c r="T130">
+        <v>1</v>
+      </c>
+      <c r="X130">
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:30">
       <c r="A131">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B131">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C131" t="s">
-        <v>496</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E131" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F131">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="G131">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I131">
         <v>1</v>
       </c>
-      <c r="L131">
-        <v>1</v>
-      </c>
-      <c r="S131">
+      <c r="U131">
         <v>1</v>
       </c>
       <c r="X131">
         <v>1</v>
       </c>
-      <c r="AA131">
+      <c r="AD131">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:30">
       <c r="A132">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B132">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C132" t="s">
-        <v>497</v>
+        <v>146</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E132" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F132">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="G132">
-        <v>2</v>
-      </c>
-      <c r="I132">
+        <v>7</v>
+      </c>
+      <c r="J132">
         <v>1</v>
       </c>
       <c r="L132">
@@ -9860,453 +9814,450 @@
         <v>1</v>
       </c>
       <c r="X132">
+        <v>1</v>
+      </c>
+      <c r="AD132">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:30">
       <c r="A133">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B133">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C133" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D133" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E133" t="s">
-        <v>146</v>
-      </c>
-      <c r="F133">
-        <v>54</v>
-      </c>
-      <c r="G133">
-        <v>4</v>
-      </c>
-      <c r="I133">
-        <v>1</v>
-      </c>
-      <c r="U133">
-        <v>1</v>
-      </c>
-      <c r="X133">
-        <v>1</v>
-      </c>
-      <c r="AD133">
-        <v>1</v>
+        <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:30">
       <c r="A134">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B134">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E134" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F134">
-        <v>45</v>
-      </c>
-      <c r="G134">
-        <v>7</v>
-      </c>
-      <c r="J134">
+        <v>68</v>
+      </c>
+      <c r="I134">
         <v>1</v>
       </c>
       <c r="L134">
         <v>1</v>
       </c>
-      <c r="T134">
+      <c r="S134">
         <v>1</v>
       </c>
       <c r="X134">
-        <v>1</v>
-      </c>
-      <c r="AD134">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:30">
       <c r="A135">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B135">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C135" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D135" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E135" t="s">
-        <v>150</v>
+        <v>153</v>
+      </c>
+      <c r="F135">
+        <v>61</v>
+      </c>
+      <c r="G135">
+        <v>3</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="S135">
+        <v>1</v>
+      </c>
+      <c r="AC135">
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:30">
       <c r="A136">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B136">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C136" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D136" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E136" t="s">
-        <v>152</v>
-      </c>
-      <c r="F136">
-        <v>68</v>
-      </c>
-      <c r="I136">
-        <v>1</v>
-      </c>
-      <c r="L136">
-        <v>1</v>
-      </c>
-      <c r="S136">
-        <v>1</v>
-      </c>
-      <c r="X136">
-        <v>1</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" spans="1:30">
       <c r="A137">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B137">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D137" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E137" t="s">
-        <v>154</v>
-      </c>
-      <c r="F137">
-        <v>61</v>
-      </c>
-      <c r="G137">
-        <v>3</v>
-      </c>
-      <c r="I137">
-        <v>1</v>
-      </c>
-      <c r="L137">
-        <v>1</v>
-      </c>
-      <c r="S137">
-        <v>1</v>
-      </c>
-      <c r="AC137">
-        <v>1</v>
+        <v>157</v>
       </c>
     </row>
     <row r="138" spans="1:30">
       <c r="A138">
+        <v>139</v>
+      </c>
+      <c r="B138">
+        <v>177</v>
+      </c>
+      <c r="C138" t="s">
+        <v>158</v>
+      </c>
+      <c r="D138" t="s">
         <v>137</v>
       </c>
-      <c r="B138">
-        <v>168</v>
-      </c>
-      <c r="C138" t="s">
-        <v>155</v>
-      </c>
-      <c r="D138" t="s">
-        <v>138</v>
-      </c>
       <c r="E138" t="s">
-        <v>156</v>
+        <v>159</v>
+      </c>
+      <c r="F138">
+        <v>61</v>
+      </c>
+      <c r="G138">
+        <v>3</v>
+      </c>
+      <c r="H138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>1</v>
+      </c>
+      <c r="Q138">
+        <v>1</v>
+      </c>
+      <c r="W138">
+        <v>1</v>
+      </c>
+      <c r="Z138">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:30">
       <c r="A139">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B139">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C139" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D139" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E139" t="s">
-        <v>158</v>
+        <v>161</v>
+      </c>
+      <c r="F139">
+        <v>67</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="T139">
+        <v>1</v>
+      </c>
+      <c r="V139">
+        <v>1</v>
+      </c>
+      <c r="X139">
+        <v>1</v>
+      </c>
+      <c r="AD139">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:30">
       <c r="A140">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B140">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C140" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E140" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F140">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G140">
-        <v>3</v>
-      </c>
-      <c r="H140">
-        <v>1</v>
-      </c>
-      <c r="K140">
-        <v>1</v>
-      </c>
-      <c r="Q140">
-        <v>1</v>
-      </c>
-      <c r="W140">
-        <v>1</v>
-      </c>
-      <c r="Z140">
+        <v>6</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="T140">
+        <v>1</v>
+      </c>
+      <c r="X140">
+        <v>1</v>
+      </c>
+      <c r="AA140">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:30">
       <c r="A141">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B141">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C141" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D141" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E141" t="s">
-        <v>162</v>
-      </c>
-      <c r="F141">
-        <v>67</v>
-      </c>
-      <c r="I141">
-        <v>1</v>
-      </c>
-      <c r="L141">
-        <v>1</v>
-      </c>
-      <c r="T141">
-        <v>1</v>
-      </c>
-      <c r="V141">
-        <v>1</v>
-      </c>
-      <c r="X141">
-        <v>1</v>
-      </c>
-      <c r="AD141">
-        <v>1</v>
+        <v>165</v>
       </c>
     </row>
     <row r="142" spans="1:30">
       <c r="A142">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B142">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C142" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E142" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F142">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G142">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I142">
         <v>1</v>
       </c>
-      <c r="M142">
+      <c r="L142">
         <v>1</v>
       </c>
       <c r="T142">
         <v>1</v>
       </c>
+      <c r="V142">
+        <v>1</v>
+      </c>
       <c r="X142">
         <v>1</v>
       </c>
-      <c r="AA142">
+      <c r="AC142">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:30">
       <c r="A143">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B143">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C143" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D143" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E143" t="s">
-        <v>166</v>
+        <v>169</v>
+      </c>
+      <c r="F143">
+        <v>78</v>
+      </c>
+      <c r="G143">
+        <v>2</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="L143">
+        <v>1</v>
+      </c>
+      <c r="T143">
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:30">
       <c r="A144">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B144">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C144" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D144" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E144" t="s">
-        <v>168</v>
-      </c>
-      <c r="F144">
-        <v>62</v>
-      </c>
-      <c r="G144">
-        <v>5</v>
-      </c>
-      <c r="I144">
-        <v>1</v>
-      </c>
-      <c r="L144">
-        <v>1</v>
-      </c>
-      <c r="T144">
-        <v>1</v>
-      </c>
-      <c r="V144">
-        <v>1</v>
-      </c>
-      <c r="X144">
-        <v>1</v>
-      </c>
-      <c r="AC144">
-        <v>1</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:29">
       <c r="A145">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B145">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C145" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D145" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E145" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F145">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G145">
-        <v>2</v>
-      </c>
-      <c r="I145">
+        <v>3</v>
+      </c>
+      <c r="J145">
         <v>1</v>
       </c>
       <c r="L145">
         <v>1</v>
       </c>
       <c r="T145">
+        <v>1</v>
+      </c>
+      <c r="X145">
+        <v>1</v>
+      </c>
+      <c r="AB145">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:29">
       <c r="A146">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B146">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C146" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D146" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E146" t="s">
-        <v>172</v>
+        <v>175</v>
+      </c>
+      <c r="F146">
+        <v>52</v>
+      </c>
+      <c r="G146">
+        <v>7</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="T146">
+        <v>1</v>
+      </c>
+      <c r="Z146">
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:29">
       <c r="A147">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B147">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C147" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D147" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E147" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F147">
-        <v>71</v>
-      </c>
-      <c r="G147">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="J147">
         <v>1</v>
       </c>
-      <c r="L147">
-        <v>1</v>
-      </c>
-      <c r="T147">
-        <v>1</v>
-      </c>
-      <c r="X147">
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="Q147">
         <v>1</v>
       </c>
       <c r="AB147">
@@ -10315,27 +10266,27 @@
     </row>
     <row r="148" spans="1:29">
       <c r="A148">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B148">
-        <v>186</v>
+        <v>272</v>
       </c>
       <c r="C148" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D148" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E148" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F148">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G148">
-        <v>7</v>
-      </c>
-      <c r="J148">
+        <v>4</v>
+      </c>
+      <c r="I148">
         <v>1</v>
       </c>
       <c r="L148">
@@ -10344,190 +10295,199 @@
       <c r="T148">
         <v>1</v>
       </c>
-      <c r="Z148">
+      <c r="X148">
+        <v>1</v>
+      </c>
+      <c r="AC148">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:29">
       <c r="A149">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B149">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C149" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D149" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
-      </c>
-      <c r="F149">
-        <v>57</v>
-      </c>
-      <c r="J149">
-        <v>1</v>
-      </c>
-      <c r="K149">
-        <v>1</v>
-      </c>
-      <c r="Q149">
-        <v>1</v>
-      </c>
-      <c r="AB149">
-        <v>1</v>
+        <v>181</v>
       </c>
     </row>
     <row r="150" spans="1:29">
       <c r="A150">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B150">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="C150" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D150" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E150" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F150">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I150">
         <v>1</v>
       </c>
-      <c r="L150">
-        <v>1</v>
-      </c>
-      <c r="T150">
-        <v>1</v>
-      </c>
-      <c r="X150">
-        <v>1</v>
-      </c>
-      <c r="AC150">
+      <c r="U150">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:29">
       <c r="A151">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B151">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C151" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D151" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E151" t="s">
-        <v>182</v>
+        <v>185</v>
+      </c>
+      <c r="F151">
+        <v>60</v>
+      </c>
+      <c r="G151">
+        <v>4</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="L151">
+        <v>1</v>
+      </c>
+      <c r="T151">
+        <v>1</v>
+      </c>
+      <c r="X151">
+        <v>1</v>
+      </c>
+      <c r="AC151">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:29">
       <c r="A152">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B152">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C152" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D152" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="E152" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F152">
-        <v>83</v>
-      </c>
-      <c r="G152">
-        <v>2</v>
-      </c>
-      <c r="I152">
-        <v>1</v>
-      </c>
-      <c r="U152">
+        <v>62</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="P152">
+        <v>1</v>
+      </c>
+      <c r="W152">
+        <v>1</v>
+      </c>
+      <c r="AC152">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:29">
       <c r="A153">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B153">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C153" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D153" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="E153" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F153">
-        <v>60</v>
-      </c>
-      <c r="G153">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="I153">
         <v>1</v>
       </c>
-      <c r="L153">
-        <v>1</v>
-      </c>
-      <c r="T153">
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="Q153">
+        <v>1</v>
+      </c>
+      <c r="V153">
         <v>1</v>
       </c>
       <c r="X153">
         <v>1</v>
       </c>
-      <c r="AC153">
+      <c r="AB153">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:29">
       <c r="A154">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B154">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C154" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D154" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E154" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F154">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="G154">
+        <v>6</v>
       </c>
       <c r="H154">
         <v>1</v>
       </c>
-      <c r="P154">
-        <v>1</v>
-      </c>
-      <c r="W154">
+      <c r="L154">
+        <v>1</v>
+      </c>
+      <c r="T154">
+        <v>1</v>
+      </c>
+      <c r="X154">
         <v>1</v>
       </c>
       <c r="AC154">
@@ -10536,916 +10496,922 @@
     </row>
     <row r="155" spans="1:29">
       <c r="A155">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B155">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C155" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D155" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E155" t="s">
-        <v>191</v>
-      </c>
-      <c r="F155">
-        <v>70</v>
-      </c>
-      <c r="I155">
-        <v>1</v>
-      </c>
-      <c r="K155">
-        <v>1</v>
-      </c>
-      <c r="Q155">
-        <v>1</v>
-      </c>
-      <c r="V155">
-        <v>1</v>
-      </c>
-      <c r="X155">
-        <v>1</v>
-      </c>
-      <c r="AB155">
-        <v>1</v>
+        <v>194</v>
       </c>
     </row>
     <row r="156" spans="1:29">
       <c r="A156">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B156">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C156" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D156" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E156" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F156">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G156">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H156">
         <v>1</v>
       </c>
-      <c r="L156">
-        <v>1</v>
-      </c>
-      <c r="T156">
-        <v>1</v>
-      </c>
-      <c r="X156">
-        <v>1</v>
-      </c>
-      <c r="AC156">
+      <c r="K156">
+        <v>1</v>
+      </c>
+      <c r="P156">
+        <v>1</v>
+      </c>
+      <c r="W156">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:29">
       <c r="A157">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B157">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C157" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D157" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E157" t="s">
-        <v>195</v>
+        <v>198</v>
+      </c>
+      <c r="F157">
+        <v>64</v>
+      </c>
+      <c r="G157">
+        <v>4</v>
+      </c>
+      <c r="H157">
+        <v>1</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="P157">
+        <v>1</v>
+      </c>
+      <c r="V157">
+        <v>1</v>
+      </c>
+      <c r="AC157">
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:29">
       <c r="A158">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B158">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C158" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D158" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E158" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F158">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G158">
-        <v>5</v>
-      </c>
-      <c r="H158">
-        <v>1</v>
-      </c>
-      <c r="K158">
-        <v>1</v>
-      </c>
-      <c r="P158">
-        <v>1</v>
-      </c>
-      <c r="W158">
+        <v>4</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="S158">
+        <v>1</v>
+      </c>
+      <c r="V158">
+        <v>1</v>
+      </c>
+      <c r="X158">
+        <v>1</v>
+      </c>
+      <c r="AA158">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:29">
       <c r="A159">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B159">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C159" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D159" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E159" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F159">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G159">
         <v>4</v>
       </c>
-      <c r="H159">
+      <c r="J159">
         <v>1</v>
       </c>
       <c r="K159">
         <v>1</v>
       </c>
-      <c r="P159">
+      <c r="Q159">
         <v>1</v>
       </c>
       <c r="V159">
         <v>1</v>
       </c>
-      <c r="AC159">
+      <c r="X159">
+        <v>1</v>
+      </c>
+      <c r="AB159">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:29">
       <c r="A160">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B160">
+        <v>205</v>
+      </c>
+      <c r="C160" t="s">
+        <v>203</v>
+      </c>
+      <c r="D160" t="s">
+        <v>186</v>
+      </c>
+      <c r="E160" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="161" spans="1:30">
+      <c r="A161">
+        <v>162</v>
+      </c>
+      <c r="B161">
+        <v>211</v>
+      </c>
+      <c r="C161" t="s">
+        <v>205</v>
+      </c>
+      <c r="D161" t="s">
+        <v>186</v>
+      </c>
+      <c r="E161" t="s">
+        <v>206</v>
+      </c>
+      <c r="F161">
+        <v>77</v>
+      </c>
+      <c r="I161">
+        <v>1</v>
+      </c>
+      <c r="S161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:30">
+      <c r="A162">
+        <v>163</v>
+      </c>
+      <c r="B162">
+        <v>217</v>
+      </c>
+      <c r="C162" t="s">
+        <v>208</v>
+      </c>
+      <c r="D162" t="s">
+        <v>207</v>
+      </c>
+      <c r="E162" t="s">
+        <v>209</v>
+      </c>
+      <c r="F162">
+        <v>57</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
+      </c>
+      <c r="Q162">
+        <v>1</v>
+      </c>
+      <c r="V162">
+        <v>1</v>
+      </c>
+      <c r="AA162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:30">
+      <c r="A163">
+        <v>164</v>
+      </c>
+      <c r="B163">
+        <v>221</v>
+      </c>
+      <c r="C163" t="s">
         <v>210</v>
       </c>
-      <c r="C160" t="s">
-        <v>200</v>
-      </c>
-      <c r="D160" t="s">
-        <v>187</v>
-      </c>
-      <c r="E160" t="s">
-        <v>201</v>
-      </c>
-      <c r="F160">
-        <v>78</v>
-      </c>
-      <c r="G160">
+      <c r="D163" t="s">
+        <v>207</v>
+      </c>
+      <c r="E163" t="s">
+        <v>211</v>
+      </c>
+      <c r="F163">
+        <v>66</v>
+      </c>
+      <c r="G163">
         <v>4</v>
       </c>
-      <c r="J160">
-        <v>1</v>
-      </c>
-      <c r="S160">
-        <v>1</v>
-      </c>
-      <c r="V160">
-        <v>1</v>
-      </c>
-      <c r="X160">
-        <v>1</v>
-      </c>
-      <c r="AA160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:29">
-      <c r="A161">
-        <v>160</v>
-      </c>
-      <c r="B161">
-        <v>239</v>
-      </c>
-      <c r="C161" t="s">
-        <v>202</v>
-      </c>
-      <c r="D161" t="s">
-        <v>187</v>
-      </c>
-      <c r="E161" t="s">
-        <v>203</v>
-      </c>
-      <c r="F161">
-        <v>60</v>
-      </c>
-      <c r="G161">
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="L163">
+        <v>1</v>
+      </c>
+      <c r="T163">
+        <v>1</v>
+      </c>
+      <c r="X163">
+        <v>1</v>
+      </c>
+      <c r="AB163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:30">
+      <c r="A164">
+        <v>165</v>
+      </c>
+      <c r="B164">
+        <v>225</v>
+      </c>
+      <c r="C164" t="s">
+        <v>212</v>
+      </c>
+      <c r="D164" t="s">
+        <v>207</v>
+      </c>
+      <c r="E164" t="s">
+        <v>213</v>
+      </c>
+      <c r="F164">
+        <v>64</v>
+      </c>
+      <c r="G164">
         <v>4</v>
       </c>
-      <c r="J161">
-        <v>1</v>
-      </c>
-      <c r="K161">
-        <v>1</v>
-      </c>
-      <c r="Q161">
-        <v>1</v>
-      </c>
-      <c r="V161">
-        <v>1</v>
-      </c>
-      <c r="X161">
-        <v>1</v>
-      </c>
-      <c r="AB161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:29">
-      <c r="A162">
-        <v>161</v>
-      </c>
-      <c r="B162">
-        <v>205</v>
-      </c>
-      <c r="C162" t="s">
-        <v>204</v>
-      </c>
-      <c r="D162" t="s">
-        <v>187</v>
-      </c>
-      <c r="E162" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="163" spans="1:29">
-      <c r="A163">
-        <v>162</v>
-      </c>
-      <c r="B163">
-        <v>211</v>
-      </c>
-      <c r="C163" t="s">
-        <v>206</v>
-      </c>
-      <c r="D163" t="s">
-        <v>187</v>
-      </c>
-      <c r="E163" t="s">
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="Q164">
+        <v>1</v>
+      </c>
+      <c r="V164">
+        <v>1</v>
+      </c>
+      <c r="AC164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:30">
+      <c r="A165">
+        <v>166</v>
+      </c>
+      <c r="B165">
+        <v>226</v>
+      </c>
+      <c r="C165" t="s">
+        <v>214</v>
+      </c>
+      <c r="D165" t="s">
         <v>207</v>
       </c>
-      <c r="F163">
-        <v>77</v>
-      </c>
-      <c r="I163">
-        <v>1</v>
-      </c>
-      <c r="S163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:29">
-      <c r="A164">
-        <v>163</v>
-      </c>
-      <c r="B164">
+      <c r="E165" t="s">
+        <v>215</v>
+      </c>
+      <c r="F165">
+        <v>65</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>1</v>
+      </c>
+      <c r="T165">
+        <v>1</v>
+      </c>
+      <c r="Y165">
+        <v>1</v>
+      </c>
+      <c r="AB165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:30">
+      <c r="A166">
+        <v>167</v>
+      </c>
+      <c r="B166">
+        <v>227</v>
+      </c>
+      <c r="C166" t="s">
+        <v>216</v>
+      </c>
+      <c r="D166" t="s">
+        <v>207</v>
+      </c>
+      <c r="E166" t="s">
         <v>217</v>
       </c>
-      <c r="C164" t="s">
-        <v>209</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="F166">
+        <v>44</v>
+      </c>
+      <c r="G166">
+        <v>5</v>
+      </c>
+      <c r="H166">
+        <v>1</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="Q166">
+        <v>1</v>
+      </c>
+      <c r="W166">
+        <v>1</v>
+      </c>
+      <c r="AB166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:30">
+      <c r="A167">
+        <v>168</v>
+      </c>
+      <c r="B167">
+        <v>218</v>
+      </c>
+      <c r="C167" t="s">
+        <v>218</v>
+      </c>
+      <c r="D167" t="s">
+        <v>207</v>
+      </c>
+      <c r="E167" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="168" spans="1:30">
+      <c r="A168">
+        <v>169</v>
+      </c>
+      <c r="B168">
+        <v>222</v>
+      </c>
+      <c r="C168" t="s">
+        <v>220</v>
+      </c>
+      <c r="D168" t="s">
+        <v>207</v>
+      </c>
+      <c r="E168" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="169" spans="1:30">
+      <c r="A169">
+        <v>170</v>
+      </c>
+      <c r="B169">
+        <v>223</v>
+      </c>
+      <c r="C169" t="s">
+        <v>222</v>
+      </c>
+      <c r="D169" t="s">
+        <v>207</v>
+      </c>
+      <c r="E169" t="s">
+        <v>223</v>
+      </c>
+      <c r="F169">
+        <v>54</v>
+      </c>
+      <c r="G169">
+        <v>4</v>
+      </c>
+      <c r="H169">
+        <v>1</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="P169">
+        <v>1</v>
+      </c>
+      <c r="V169">
+        <v>1</v>
+      </c>
+      <c r="AB169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:30">
+      <c r="A170">
+        <v>171</v>
+      </c>
+      <c r="B170">
+        <v>220</v>
+      </c>
+      <c r="C170" t="s">
+        <v>224</v>
+      </c>
+      <c r="D170" t="s">
+        <v>207</v>
+      </c>
+      <c r="E170" t="s">
+        <v>225</v>
+      </c>
+      <c r="F170">
+        <v>63</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q170">
+        <v>1</v>
+      </c>
+      <c r="V170">
+        <v>1</v>
+      </c>
+      <c r="X170">
+        <v>1</v>
+      </c>
+      <c r="AB170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:30">
+      <c r="A171">
+        <v>172</v>
+      </c>
+      <c r="B171">
+        <v>229</v>
+      </c>
+      <c r="C171" t="s">
+        <v>226</v>
+      </c>
+      <c r="D171" t="s">
+        <v>207</v>
+      </c>
+      <c r="E171" t="s">
+        <v>227</v>
+      </c>
+      <c r="F171">
+        <v>68</v>
+      </c>
+      <c r="G171">
+        <v>3</v>
+      </c>
+      <c r="H171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="R171">
+        <v>1</v>
+      </c>
+      <c r="T171">
+        <v>1</v>
+      </c>
+      <c r="V171">
+        <v>1</v>
+      </c>
+      <c r="X171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:30">
+      <c r="A172">
+        <v>173</v>
+      </c>
+      <c r="B172">
         <v>208</v>
       </c>
-      <c r="E164" t="s">
-        <v>210</v>
-      </c>
-      <c r="F164">
-        <v>57</v>
-      </c>
-      <c r="J164">
-        <v>1</v>
-      </c>
-      <c r="K164">
-        <v>1</v>
-      </c>
-      <c r="Q164">
-        <v>1</v>
-      </c>
-      <c r="V164">
-        <v>1</v>
-      </c>
-      <c r="AA164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:29">
-      <c r="A165">
-        <v>164</v>
-      </c>
-      <c r="B165">
-        <v>221</v>
-      </c>
-      <c r="C165" t="s">
-        <v>211</v>
-      </c>
-      <c r="D165" t="s">
-        <v>208</v>
-      </c>
-      <c r="E165" t="s">
-        <v>212</v>
-      </c>
-      <c r="F165">
-        <v>66</v>
-      </c>
-      <c r="G165">
-        <v>4</v>
-      </c>
-      <c r="I165">
-        <v>1</v>
-      </c>
-      <c r="L165">
-        <v>1</v>
-      </c>
-      <c r="T165">
-        <v>1</v>
-      </c>
-      <c r="X165">
-        <v>1</v>
-      </c>
-      <c r="AB165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:29">
-      <c r="A166">
-        <v>165</v>
-      </c>
-      <c r="B166">
-        <v>225</v>
-      </c>
-      <c r="C166" t="s">
+      <c r="C172" t="s">
+        <v>228</v>
+      </c>
+      <c r="D172" t="s">
+        <v>186</v>
+      </c>
+      <c r="E172" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="173" spans="1:30">
+      <c r="A173">
+        <v>174</v>
+      </c>
+      <c r="B173">
+        <v>214</v>
+      </c>
+      <c r="C173" t="s">
+        <v>230</v>
+      </c>
+      <c r="D173" t="s">
+        <v>186</v>
+      </c>
+      <c r="E173" t="s">
+        <v>231</v>
+      </c>
+      <c r="F173">
+        <v>70</v>
+      </c>
+      <c r="G173">
+        <v>2</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173" t="s">
+        <v>500</v>
+      </c>
+      <c r="O173" t="s">
+        <v>501</v>
+      </c>
+      <c r="Y173">
+        <v>1</v>
+      </c>
+      <c r="Z173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:30">
+      <c r="A174">
+        <v>175</v>
+      </c>
+      <c r="B174">
+        <v>215</v>
+      </c>
+      <c r="C174" t="s">
+        <v>232</v>
+      </c>
+      <c r="D174" t="s">
+        <v>186</v>
+      </c>
+      <c r="E174" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="175" spans="1:30">
+      <c r="A175">
+        <v>176</v>
+      </c>
+      <c r="B175">
         <v>213</v>
       </c>
-      <c r="D166" t="s">
-        <v>208</v>
-      </c>
-      <c r="E166" t="s">
-        <v>214</v>
-      </c>
-      <c r="F166">
-        <v>64</v>
-      </c>
-      <c r="G166">
-        <v>4</v>
-      </c>
-      <c r="I166">
-        <v>1</v>
-      </c>
-      <c r="K166">
-        <v>1</v>
-      </c>
-      <c r="Q166">
-        <v>1</v>
-      </c>
-      <c r="V166">
-        <v>1</v>
-      </c>
-      <c r="AC166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:29">
-      <c r="A167">
-        <v>166</v>
-      </c>
-      <c r="B167">
-        <v>226</v>
-      </c>
-      <c r="C167" t="s">
-        <v>215</v>
-      </c>
-      <c r="D167" t="s">
-        <v>208</v>
-      </c>
-      <c r="E167" t="s">
-        <v>216</v>
-      </c>
-      <c r="F167">
-        <v>65</v>
-      </c>
-      <c r="J167">
-        <v>1</v>
-      </c>
-      <c r="M167">
-        <v>1</v>
-      </c>
-      <c r="T167">
-        <v>1</v>
-      </c>
-      <c r="Y167">
-        <v>1</v>
-      </c>
-      <c r="AB167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:29">
-      <c r="A168">
-        <v>167</v>
-      </c>
-      <c r="B168">
-        <v>227</v>
-      </c>
-      <c r="C168" t="s">
-        <v>217</v>
-      </c>
-      <c r="D168" t="s">
-        <v>208</v>
-      </c>
-      <c r="E168" t="s">
-        <v>218</v>
-      </c>
-      <c r="F168">
-        <v>44</v>
-      </c>
-      <c r="G168">
-        <v>5</v>
-      </c>
-      <c r="H168">
-        <v>1</v>
-      </c>
-      <c r="K168">
-        <v>1</v>
-      </c>
-      <c r="Q168">
-        <v>1</v>
-      </c>
-      <c r="W168">
-        <v>1</v>
-      </c>
-      <c r="AB168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:29">
-      <c r="A169">
-        <v>168</v>
-      </c>
-      <c r="B169">
-        <v>218</v>
-      </c>
-      <c r="C169" t="s">
-        <v>219</v>
-      </c>
-      <c r="D169" t="s">
-        <v>208</v>
-      </c>
-      <c r="E169" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="170" spans="1:29">
-      <c r="A170">
-        <v>169</v>
-      </c>
-      <c r="B170">
-        <v>222</v>
-      </c>
-      <c r="C170" t="s">
-        <v>221</v>
-      </c>
-      <c r="D170" t="s">
-        <v>208</v>
-      </c>
-      <c r="E170" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="171" spans="1:29">
-      <c r="A171">
-        <v>170</v>
-      </c>
-      <c r="B171">
-        <v>223</v>
-      </c>
-      <c r="C171" t="s">
-        <v>223</v>
-      </c>
-      <c r="D171" t="s">
-        <v>208</v>
-      </c>
-      <c r="E171" t="s">
+      <c r="C175" t="s">
+        <v>234</v>
+      </c>
+      <c r="D175" t="s">
+        <v>186</v>
+      </c>
+      <c r="E175" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="176" spans="1:30">
+      <c r="A176">
+        <v>177</v>
+      </c>
+      <c r="B176">
         <v>224</v>
       </c>
-      <c r="F171">
-        <v>54</v>
-      </c>
-      <c r="G171">
-        <v>4</v>
-      </c>
-      <c r="H171">
-        <v>1</v>
-      </c>
-      <c r="K171">
-        <v>1</v>
-      </c>
-      <c r="P171">
-        <v>1</v>
-      </c>
-      <c r="V171">
-        <v>1</v>
-      </c>
-      <c r="AB171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:29">
-      <c r="A172">
-        <v>171</v>
-      </c>
-      <c r="B172">
-        <v>220</v>
-      </c>
-      <c r="C172" t="s">
-        <v>225</v>
-      </c>
-      <c r="D172" t="s">
-        <v>208</v>
-      </c>
-      <c r="E172" t="s">
-        <v>226</v>
-      </c>
-      <c r="F172">
-        <v>63</v>
-      </c>
-      <c r="I172">
-        <v>1</v>
-      </c>
-      <c r="M172">
-        <v>1</v>
-      </c>
-      <c r="O172" t="s">
-        <v>514</v>
-      </c>
-      <c r="Q172">
-        <v>1</v>
-      </c>
-      <c r="V172">
-        <v>1</v>
-      </c>
-      <c r="X172">
-        <v>1</v>
-      </c>
-      <c r="AB172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:29">
-      <c r="A173">
-        <v>172</v>
-      </c>
-      <c r="B173">
-        <v>229</v>
-      </c>
-      <c r="C173" t="s">
-        <v>227</v>
-      </c>
-      <c r="D173" t="s">
-        <v>208</v>
-      </c>
-      <c r="E173" t="s">
-        <v>228</v>
-      </c>
-      <c r="F173">
-        <v>68</v>
-      </c>
-      <c r="G173">
-        <v>3</v>
-      </c>
-      <c r="H173">
-        <v>1</v>
-      </c>
-      <c r="K173">
-        <v>1</v>
-      </c>
-      <c r="R173">
-        <v>1</v>
-      </c>
-      <c r="T173">
-        <v>1</v>
-      </c>
-      <c r="V173">
-        <v>1</v>
-      </c>
-      <c r="X173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:29">
-      <c r="A174">
-        <v>173</v>
-      </c>
-      <c r="B174">
-        <v>208</v>
-      </c>
-      <c r="C174" t="s">
-        <v>229</v>
-      </c>
-      <c r="D174" t="s">
-        <v>187</v>
-      </c>
-      <c r="E174" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="175" spans="1:29">
-      <c r="A175">
-        <v>174</v>
-      </c>
-      <c r="B175">
-        <v>214</v>
-      </c>
-      <c r="C175" t="s">
-        <v>231</v>
-      </c>
-      <c r="D175" t="s">
-        <v>187</v>
-      </c>
-      <c r="E175" t="s">
-        <v>232</v>
-      </c>
-      <c r="F175">
+      <c r="C176" t="s">
+        <v>236</v>
+      </c>
+      <c r="D176" t="s">
+        <v>186</v>
+      </c>
+      <c r="E176" t="s">
+        <v>237</v>
+      </c>
+      <c r="F176">
         <v>70</v>
       </c>
-      <c r="G175">
+      <c r="G176">
         <v>2</v>
       </c>
-      <c r="M175">
-        <v>1</v>
-      </c>
-      <c r="N175" t="s">
-        <v>507</v>
-      </c>
-      <c r="O175" t="s">
-        <v>508</v>
-      </c>
-      <c r="Y175">
-        <v>1</v>
-      </c>
-      <c r="Z175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:29">
-      <c r="A176">
-        <v>175</v>
-      </c>
-      <c r="B176">
-        <v>215</v>
-      </c>
-      <c r="C176" t="s">
-        <v>233</v>
-      </c>
-      <c r="D176" t="s">
-        <v>187</v>
-      </c>
-      <c r="E176" t="s">
-        <v>234</v>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="Q176">
+        <v>1</v>
+      </c>
+      <c r="AD176">
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:30">
       <c r="A177">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B177">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C177" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D177" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E177" t="s">
-        <v>236</v>
+        <v>239</v>
+      </c>
+      <c r="F177">
+        <v>49</v>
+      </c>
+      <c r="G177">
+        <v>6</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="M177">
+        <v>1</v>
+      </c>
+      <c r="U177">
+        <v>1</v>
+      </c>
+      <c r="AC177">
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:30">
       <c r="A178">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B178">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C178" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D178" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E178" t="s">
-        <v>238</v>
-      </c>
-      <c r="F178">
-        <v>70</v>
-      </c>
-      <c r="G178">
-        <v>2</v>
-      </c>
-      <c r="I178">
-        <v>1</v>
-      </c>
-      <c r="L178">
-        <v>1</v>
-      </c>
-      <c r="Q178">
-        <v>1</v>
-      </c>
-      <c r="AD178">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="179" spans="1:30">
       <c r="A179">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B179">
-        <v>203</v>
+        <v>85</v>
       </c>
       <c r="C179" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D179" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="E179" t="s">
-        <v>240</v>
-      </c>
-      <c r="F179">
-        <v>49</v>
-      </c>
-      <c r="G179">
-        <v>6</v>
-      </c>
-      <c r="I179">
-        <v>1</v>
-      </c>
-      <c r="M179">
-        <v>1</v>
-      </c>
-      <c r="U179">
-        <v>1</v>
-      </c>
-      <c r="AC179">
-        <v>1</v>
+        <v>243</v>
       </c>
     </row>
     <row r="180" spans="1:30">
       <c r="A180">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B180">
-        <v>206</v>
+        <v>6</v>
       </c>
       <c r="C180" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D180" t="s">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="E180" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="181" spans="1:30">
       <c r="A181">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B181">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C181" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D181" t="s">
         <v>39</v>
       </c>
       <c r="E181" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="182" spans="1:30">
       <c r="A182">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B182">
-        <v>6</v>
+        <v>78</v>
       </c>
       <c r="C182" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D182" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E182" t="s">
-        <v>246</v>
+        <v>65</v>
+      </c>
+      <c r="F182">
+        <v>59</v>
+      </c>
+      <c r="I182">
+        <v>1</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182" t="s">
+        <v>500</v>
+      </c>
+      <c r="O182" t="s">
+        <v>501</v>
+      </c>
+      <c r="U182">
+        <v>1</v>
+      </c>
+      <c r="AC182">
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:30">
       <c r="A183">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B183">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="C183" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D183" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E183" t="s">
-        <v>244</v>
+        <v>249</v>
+      </c>
+      <c r="F183">
+        <v>78</v>
+      </c>
+      <c r="G183">
+        <v>4</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="L183">
+        <v>1</v>
+      </c>
+      <c r="T183">
+        <v>1</v>
+      </c>
+      <c r="V183">
+        <v>1</v>
+      </c>
+      <c r="X183">
+        <v>1</v>
+      </c>
+      <c r="AA183">
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:30">
       <c r="A184">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B184">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="C184" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D184" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E184" t="s">
-        <v>66</v>
+        <v>251</v>
       </c>
       <c r="F184">
-        <v>59</v>
+        <v>89</v>
+      </c>
+      <c r="G184">
+        <v>2</v>
       </c>
       <c r="I184">
         <v>1</v>
       </c>
-      <c r="M184">
-        <v>1</v>
-      </c>
-      <c r="N184" t="s">
-        <v>507</v>
-      </c>
-      <c r="O184" t="s">
-        <v>508</v>
-      </c>
-      <c r="U184">
-        <v>1</v>
-      </c>
-      <c r="AC184">
+      <c r="L184">
+        <v>1</v>
+      </c>
+      <c r="T184">
+        <v>1</v>
+      </c>
+      <c r="V184">
+        <v>1</v>
+      </c>
+      <c r="X184">
+        <v>1</v>
+      </c>
+      <c r="AA184">
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:30">
       <c r="A185">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B185">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="C185" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D185" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="E185" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F185">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G185">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I185">
         <v>1</v>
@@ -11453,40 +11419,37 @@
       <c r="L185">
         <v>1</v>
       </c>
-      <c r="T185">
-        <v>1</v>
-      </c>
-      <c r="V185">
+      <c r="U185">
         <v>1</v>
       </c>
       <c r="X185">
         <v>1</v>
       </c>
-      <c r="AA185">
+      <c r="AC185">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:30">
       <c r="A186">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B186">
-        <v>17</v>
+        <v>197</v>
       </c>
       <c r="C186" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D186" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="E186" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F186">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G186">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I186">
         <v>1</v>
@@ -11494,261 +11457,234 @@
       <c r="L186">
         <v>1</v>
       </c>
-      <c r="T186">
-        <v>1</v>
-      </c>
-      <c r="V186">
+      <c r="U186">
         <v>1</v>
       </c>
       <c r="X186">
         <v>1</v>
       </c>
-      <c r="AA186">
+      <c r="AD186">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:30">
       <c r="A187">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B187">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="C187" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D187" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="E187" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F187">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G187">
-        <v>2</v>
-      </c>
-      <c r="I187">
+        <v>5</v>
+      </c>
+      <c r="J187">
         <v>1</v>
       </c>
       <c r="L187">
         <v>1</v>
       </c>
-      <c r="U187">
+      <c r="Q187">
+        <v>1</v>
+      </c>
+      <c r="T187">
+        <v>1</v>
+      </c>
+      <c r="W187">
         <v>1</v>
       </c>
       <c r="X187">
         <v>1</v>
       </c>
-      <c r="AC187">
+      <c r="Z187">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:30">
       <c r="A188">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B188">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C188" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D188" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E188" t="s">
-        <v>256</v>
-      </c>
-      <c r="F188">
-        <v>78</v>
-      </c>
-      <c r="G188">
-        <v>5</v>
-      </c>
-      <c r="I188">
-        <v>1</v>
-      </c>
-      <c r="L188">
-        <v>1</v>
-      </c>
-      <c r="U188">
-        <v>1</v>
-      </c>
-      <c r="X188">
-        <v>1</v>
-      </c>
-      <c r="AD188">
-        <v>1</v>
+        <v>259</v>
       </c>
     </row>
     <row r="189" spans="1:30">
       <c r="A189">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B189">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="C189" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D189" t="s">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="E189" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F189">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="G189">
-        <v>5</v>
-      </c>
-      <c r="J189">
-        <v>1</v>
-      </c>
-      <c r="L189">
-        <v>1</v>
-      </c>
-      <c r="Q189">
-        <v>1</v>
-      </c>
-      <c r="T189">
-        <v>1</v>
-      </c>
-      <c r="W189">
-        <v>1</v>
-      </c>
-      <c r="X189">
-        <v>1</v>
-      </c>
-      <c r="Z189">
+        <v>2</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="U189">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:30">
       <c r="A190">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B190">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D190" t="s">
-        <v>187</v>
+        <v>137</v>
       </c>
       <c r="E190" t="s">
-        <v>260</v>
+        <v>263</v>
+      </c>
+      <c r="F190">
+        <v>59</v>
+      </c>
+      <c r="G190">
+        <v>3</v>
+      </c>
+      <c r="I190">
+        <v>1</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190" t="s">
+        <v>500</v>
+      </c>
+      <c r="O190" t="s">
+        <v>501</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="AD190">
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:30">
       <c r="A191">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B191">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E191" t="s">
-        <v>262</v>
-      </c>
-      <c r="F191">
-        <v>76</v>
-      </c>
-      <c r="G191">
-        <v>2</v>
-      </c>
-      <c r="I191">
-        <v>1</v>
-      </c>
-      <c r="U191">
-        <v>1</v>
+        <v>265</v>
       </c>
     </row>
     <row r="192" spans="1:30">
       <c r="A192">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B192">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="C192" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="E192" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F192">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I192">
         <v>1</v>
       </c>
-      <c r="M192">
-        <v>1</v>
-      </c>
-      <c r="N192" t="s">
-        <v>507</v>
-      </c>
-      <c r="O192" t="s">
-        <v>508</v>
-      </c>
-      <c r="T192">
-        <v>1</v>
-      </c>
-      <c r="AD192">
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="S192">
+        <v>1</v>
+      </c>
+      <c r="X192">
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:30">
       <c r="A193">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B193">
-        <v>188</v>
+        <v>273</v>
       </c>
       <c r="C193" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D193" t="s">
-        <v>138</v>
+        <v>6</v>
       </c>
       <c r="E193" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="194" spans="1:30">
       <c r="A194">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B194">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="C194" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D194" t="s">
-        <v>39</v>
+        <v>186</v>
       </c>
       <c r="E194" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F194">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="G194">
         <v>2</v>
@@ -11756,167 +11692,208 @@
       <c r="I194">
         <v>1</v>
       </c>
-      <c r="L194">
-        <v>1</v>
-      </c>
-      <c r="S194">
-        <v>1</v>
-      </c>
-      <c r="X194">
-        <v>1</v>
+      <c r="M194">
+        <v>1</v>
+      </c>
+      <c r="N194" t="s">
+        <v>508</v>
+      </c>
+      <c r="O194" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="195" spans="1:30">
       <c r="A195">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B195">
+        <v>228</v>
+      </c>
+      <c r="C195" t="s">
+        <v>272</v>
+      </c>
+      <c r="D195" t="s">
+        <v>186</v>
+      </c>
+      <c r="E195" t="s">
         <v>273</v>
-      </c>
-      <c r="C195" t="s">
-        <v>269</v>
-      </c>
-      <c r="D195" t="s">
-        <v>6</v>
-      </c>
-      <c r="E195" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="196" spans="1:30">
       <c r="A196">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B196">
-        <v>230</v>
+        <v>56</v>
       </c>
       <c r="C196" t="s">
-        <v>271</v>
+        <v>532</v>
       </c>
       <c r="D196" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="E196" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F196">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G196">
-        <v>2</v>
-      </c>
-      <c r="I196">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M196">
         <v>1</v>
       </c>
       <c r="N196" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="O196" t="s">
-        <v>516</v>
+        <v>509</v>
+      </c>
+      <c r="T196">
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:30">
       <c r="A197">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B197">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="C197" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D197" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E197" t="s">
-        <v>274</v>
+        <v>277</v>
+      </c>
+      <c r="F197">
+        <v>42</v>
+      </c>
+      <c r="G197">
+        <v>5</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="L197">
+        <v>1</v>
+      </c>
+      <c r="T197">
+        <v>1</v>
+      </c>
+      <c r="X197">
+        <v>1</v>
+      </c>
+      <c r="AD197">
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:30">
       <c r="A198">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B198">
-        <v>56</v>
+        <v>261</v>
       </c>
       <c r="C198" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D198" t="s">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="E198" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F198">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="G198">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="J198">
+        <v>1</v>
       </c>
       <c r="M198">
         <v>1</v>
       </c>
       <c r="N198" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="O198" t="s">
-        <v>516</v>
-      </c>
-      <c r="T198">
-        <v>1</v>
+        <v>501</v>
       </c>
     </row>
     <row r="199" spans="1:30">
-      <c r="A199" s="1">
-        <v>198</v>
-      </c>
-      <c r="B199" s="1">
-        <v>40</v>
-      </c>
-      <c r="C199" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F199" s="1"/>
+      <c r="A199">
+        <v>201</v>
+      </c>
+      <c r="B199">
+        <v>38</v>
+      </c>
+      <c r="C199" t="s">
+        <v>280</v>
+      </c>
+      <c r="D199" t="s">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>281</v>
+      </c>
+      <c r="F199">
+        <v>45</v>
+      </c>
+      <c r="G199">
+        <v>6</v>
+      </c>
+      <c r="I199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="Z199">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" spans="1:30">
       <c r="A200">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B200">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="C200" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D200" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="E200" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F200">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="G200">
-        <v>5</v>
-      </c>
-      <c r="I200">
+        <v>9</v>
+      </c>
+      <c r="H200">
         <v>1</v>
       </c>
       <c r="L200">
         <v>1</v>
       </c>
       <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="V200">
         <v>1</v>
       </c>
       <c r="X200">
@@ -11928,754 +11905,757 @@
     </row>
     <row r="201" spans="1:30">
       <c r="A201">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B201">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C201" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D201" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E201" t="s">
-        <v>282</v>
-      </c>
-      <c r="F201">
-        <v>76</v>
-      </c>
-      <c r="G201">
-        <v>6</v>
-      </c>
-      <c r="J201">
-        <v>1</v>
-      </c>
-      <c r="M201">
-        <v>1</v>
-      </c>
-      <c r="N201" t="s">
-        <v>507</v>
-      </c>
-      <c r="O201" t="s">
-        <v>508</v>
+        <v>285</v>
       </c>
     </row>
     <row r="202" spans="1:30">
       <c r="A202">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B202">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="C202" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D202" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E202" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F202">
-        <v>45</v>
-      </c>
-      <c r="G202">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="I202">
         <v>1</v>
       </c>
-      <c r="L202">
-        <v>1</v>
+      <c r="M202">
+        <v>1</v>
+      </c>
+      <c r="N202" t="s">
+        <v>502</v>
+      </c>
+      <c r="O202" t="s">
+        <v>504</v>
       </c>
       <c r="T202">
-        <v>1</v>
-      </c>
-      <c r="Z202">
         <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:30">
       <c r="A203">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B203">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C203" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D203" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E203" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F203">
-        <v>61</v>
-      </c>
-      <c r="G203">
-        <v>9</v>
-      </c>
-      <c r="H203">
+        <v>59</v>
+      </c>
+      <c r="I203">
         <v>1</v>
       </c>
       <c r="L203">
         <v>1</v>
       </c>
-      <c r="T203">
-        <v>1</v>
-      </c>
-      <c r="V203">
+      <c r="U203">
         <v>1</v>
       </c>
       <c r="X203">
         <v>1</v>
       </c>
-      <c r="AD203">
+      <c r="AC203">
         <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:30">
       <c r="A204">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B204">
-        <v>274</v>
+        <v>231</v>
       </c>
       <c r="C204" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D204" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E204" t="s">
-        <v>288</v>
+        <v>291</v>
+      </c>
+      <c r="F204">
+        <v>69</v>
+      </c>
+      <c r="G204">
+        <v>5</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="L204">
+        <v>1</v>
+      </c>
+      <c r="T204">
+        <v>1</v>
+      </c>
+      <c r="X204">
+        <v>1</v>
+      </c>
+      <c r="AC204">
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:30">
       <c r="A205">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B205">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="C205" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D205" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="E205" t="s">
-        <v>290</v>
-      </c>
-      <c r="F205">
-        <v>81</v>
-      </c>
-      <c r="I205">
-        <v>1</v>
-      </c>
-      <c r="M205">
-        <v>1</v>
-      </c>
-      <c r="N205" t="s">
-        <v>509</v>
-      </c>
-      <c r="O205" t="s">
-        <v>511</v>
-      </c>
-      <c r="T205">
-        <v>1</v>
+        <v>293</v>
       </c>
     </row>
     <row r="206" spans="1:30">
       <c r="A206">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B206">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C206" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D206" t="s">
         <v>6</v>
       </c>
       <c r="E206" t="s">
-        <v>292</v>
-      </c>
-      <c r="F206">
-        <v>59</v>
-      </c>
-      <c r="I206">
-        <v>1</v>
-      </c>
-      <c r="L206">
-        <v>1</v>
-      </c>
-      <c r="U206">
-        <v>1</v>
-      </c>
-      <c r="X206">
-        <v>1</v>
-      </c>
-      <c r="AC206">
-        <v>1</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:30">
       <c r="A207">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B207">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="C207" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D207" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="E207" t="s">
-        <v>294</v>
-      </c>
-      <c r="F207">
-        <v>69</v>
-      </c>
-      <c r="G207">
-        <v>5</v>
-      </c>
-      <c r="I207">
-        <v>1</v>
-      </c>
-      <c r="L207">
-        <v>1</v>
-      </c>
-      <c r="T207">
-        <v>1</v>
-      </c>
-      <c r="X207">
-        <v>1</v>
-      </c>
-      <c r="AC207">
-        <v>1</v>
+        <v>297</v>
       </c>
     </row>
     <row r="208" spans="1:30">
       <c r="A208">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B208">
-        <v>150</v>
+        <v>276</v>
       </c>
       <c r="C208" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D208" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E208" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="F208">
+        <v>41</v>
+      </c>
+      <c r="G208">
+        <v>6</v>
+      </c>
+      <c r="J208">
+        <v>1</v>
+      </c>
+      <c r="L208">
+        <v>1</v>
+      </c>
+      <c r="N208" t="s">
+        <v>505</v>
+      </c>
+      <c r="O208" t="s">
+        <v>510</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="AD208">
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:30">
       <c r="A209">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B209">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="C209" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D209" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="E209" t="s">
-        <v>297</v>
+        <v>300</v>
+      </c>
+      <c r="F209">
+        <v>45</v>
+      </c>
+      <c r="G209">
+        <v>2</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>1</v>
+      </c>
+      <c r="AD209">
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:30">
       <c r="A210">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B210">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C210" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D210" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E210" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="211" spans="1:30">
       <c r="A211">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B211">
-        <v>275</v>
+        <v>106</v>
       </c>
       <c r="C211" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D211" t="s">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E211" t="s">
-        <v>301</v>
+        <v>304</v>
+      </c>
+      <c r="F211">
+        <v>59</v>
+      </c>
+      <c r="G211">
+        <v>7</v>
+      </c>
+      <c r="J211">
+        <v>1</v>
+      </c>
+      <c r="L211">
+        <v>1</v>
+      </c>
+      <c r="U211">
+        <v>1</v>
+      </c>
+      <c r="X211">
+        <v>1</v>
+      </c>
+      <c r="AD211">
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:30">
       <c r="A212">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B212">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C212" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D212" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E212" t="s">
-        <v>118</v>
+        <v>306</v>
       </c>
       <c r="F212">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G212">
-        <v>6</v>
-      </c>
-      <c r="J212">
+        <v>5</v>
+      </c>
+      <c r="I212">
         <v>1</v>
       </c>
       <c r="L212">
         <v>1</v>
       </c>
-      <c r="N212" t="s">
-        <v>512</v>
-      </c>
-      <c r="O212" t="s">
-        <v>517</v>
-      </c>
       <c r="T212">
         <v>1</v>
       </c>
-      <c r="AD212">
+      <c r="X212">
+        <v>1</v>
+      </c>
+      <c r="Z212">
         <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:30">
       <c r="A213">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B213">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C213" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D213" t="s">
-        <v>107</v>
+        <v>186</v>
       </c>
       <c r="E213" t="s">
-        <v>304</v>
-      </c>
-      <c r="F213">
-        <v>45</v>
-      </c>
-      <c r="G213">
-        <v>2</v>
-      </c>
-      <c r="I213">
-        <v>1</v>
-      </c>
-      <c r="L213">
-        <v>1</v>
-      </c>
-      <c r="T213">
-        <v>1</v>
-      </c>
-      <c r="AD213">
-        <v>1</v>
+        <v>198</v>
       </c>
     </row>
     <row r="214" spans="1:30">
       <c r="A214">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B214">
-        <v>103</v>
+        <v>280</v>
       </c>
       <c r="C214" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D214" t="s">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="E214" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="215" spans="1:30">
       <c r="A215">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B215">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="C215" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D215" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="E215" t="s">
-        <v>308</v>
+        <v>37</v>
       </c>
     </row>
     <row r="216" spans="1:30">
       <c r="A216">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B216">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="C216" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D216" t="s">
-        <v>83</v>
+        <v>186</v>
       </c>
       <c r="E216" t="s">
-        <v>310</v>
-      </c>
-      <c r="F216">
-        <v>59</v>
-      </c>
-      <c r="G216">
-        <v>7</v>
-      </c>
-      <c r="J216">
-        <v>1</v>
-      </c>
-      <c r="L216">
-        <v>1</v>
-      </c>
-      <c r="U216">
-        <v>1</v>
-      </c>
-      <c r="X216">
-        <v>1</v>
-      </c>
-      <c r="AD216">
-        <v>1</v>
+        <v>241</v>
       </c>
     </row>
     <row r="217" spans="1:30">
       <c r="A217">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B217">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="C217" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D217" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="E217" t="s">
-        <v>312</v>
-      </c>
-      <c r="F217">
-        <v>55</v>
-      </c>
-      <c r="G217">
-        <v>5</v>
-      </c>
-      <c r="I217">
-        <v>1</v>
-      </c>
-      <c r="L217">
-        <v>1</v>
-      </c>
-      <c r="T217">
-        <v>1</v>
-      </c>
-      <c r="X217">
-        <v>1</v>
-      </c>
-      <c r="Z217">
-        <v>1</v>
+        <v>314</v>
       </c>
     </row>
     <row r="218" spans="1:30">
       <c r="A218">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B218">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C218" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D218" t="s">
-        <v>187</v>
+        <v>6</v>
       </c>
       <c r="E218" t="s">
-        <v>199</v>
+        <v>316</v>
       </c>
     </row>
     <row r="219" spans="1:30">
       <c r="A219">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B219">
-        <v>280</v>
+        <v>234</v>
       </c>
       <c r="C219" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D219" t="s">
-        <v>314</v>
+        <v>207</v>
       </c>
       <c r="E219" t="s">
-        <v>316</v>
+        <v>318</v>
+      </c>
+      <c r="F219">
+        <v>65</v>
+      </c>
+      <c r="G219">
+        <v>3</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="V219">
+        <v>1</v>
+      </c>
+      <c r="X219">
+        <v>1</v>
+      </c>
+      <c r="AD219">
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:30">
       <c r="A220">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B220">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C220" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D220" t="s">
+        <v>319</v>
+      </c>
+      <c r="E220" t="s">
+        <v>321</v>
+      </c>
+      <c r="F220">
+        <v>55</v>
+      </c>
+      <c r="G220">
         <v>6</v>
       </c>
-      <c r="E220" t="s">
-        <v>37</v>
+      <c r="H220">
+        <v>1</v>
+      </c>
+      <c r="L220">
+        <v>1</v>
+      </c>
+      <c r="T220">
+        <v>1</v>
+      </c>
+      <c r="V220">
+        <v>1</v>
+      </c>
+      <c r="X220">
+        <v>1</v>
+      </c>
+      <c r="AC220">
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:30">
       <c r="A221">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B221">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C221" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D221" t="s">
-        <v>187</v>
+        <v>322</v>
       </c>
       <c r="E221" t="s">
-        <v>242</v>
+        <v>324</v>
+      </c>
+      <c r="F221">
+        <v>58</v>
+      </c>
+      <c r="G221">
+        <v>4</v>
+      </c>
+      <c r="I221">
+        <v>1</v>
+      </c>
+      <c r="M221">
+        <v>1</v>
+      </c>
+      <c r="N221" t="s">
+        <v>502</v>
+      </c>
+      <c r="O221" t="s">
+        <v>511</v>
+      </c>
+      <c r="U221">
+        <v>1</v>
+      </c>
+      <c r="X221">
+        <v>1</v>
+      </c>
+      <c r="Z221">
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:30">
       <c r="A222">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B222">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="C222" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="D222" t="s">
-        <v>39</v>
+        <v>325</v>
       </c>
       <c r="E222" t="s">
-        <v>320</v>
+        <v>327</v>
+      </c>
+      <c r="F222">
+        <v>57</v>
+      </c>
+      <c r="G222">
+        <v>8</v>
+      </c>
+      <c r="H222">
+        <v>1</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+      <c r="P222">
+        <v>1</v>
+      </c>
+      <c r="W222">
+        <v>1</v>
+      </c>
+      <c r="Z222">
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:30">
       <c r="A223">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B223">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="C223" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D223" t="s">
-        <v>6</v>
+        <v>328</v>
       </c>
       <c r="E223" t="s">
-        <v>322</v>
+        <v>329</v>
+      </c>
+      <c r="F223">
+        <v>48</v>
+      </c>
+      <c r="G223">
+        <v>3</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="Q223">
+        <v>1</v>
+      </c>
+      <c r="U223">
+        <v>1</v>
+      </c>
+      <c r="AC223">
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:30">
       <c r="A224">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B224">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C224" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>330</v>
       </c>
       <c r="E224" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F224">
-        <v>65</v>
-      </c>
-      <c r="G224">
-        <v>3</v>
-      </c>
-      <c r="I224">
-        <v>1</v>
-      </c>
-      <c r="L224">
-        <v>1</v>
-      </c>
-      <c r="T224">
-        <v>1</v>
-      </c>
-      <c r="V224">
-        <v>1</v>
-      </c>
-      <c r="X224">
-        <v>1</v>
-      </c>
-      <c r="AD224">
+        <v>43</v>
+      </c>
+      <c r="H224">
+        <v>1</v>
+      </c>
+      <c r="K224">
+        <v>1</v>
+      </c>
+      <c r="P224">
+        <v>1</v>
+      </c>
+      <c r="W224">
+        <v>1</v>
+      </c>
+      <c r="AA224">
         <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:30">
       <c r="A225">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B225">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="C225" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D225" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E225" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="F225">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G225">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H225">
-        <v>1</v>
-      </c>
-      <c r="L225">
-        <v>1</v>
-      </c>
-      <c r="T225">
-        <v>1</v>
-      </c>
-      <c r="V225">
-        <v>1</v>
-      </c>
-      <c r="X225">
-        <v>1</v>
-      </c>
-      <c r="AC225">
         <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:30">
       <c r="A226">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B226">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C226" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D226" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="E226" t="s">
-        <v>330</v>
-      </c>
-      <c r="F226">
-        <v>58</v>
-      </c>
-      <c r="G226">
-        <v>4</v>
-      </c>
-      <c r="I226">
-        <v>1</v>
-      </c>
-      <c r="M226">
-        <v>1</v>
-      </c>
-      <c r="N226" t="s">
-        <v>509</v>
-      </c>
-      <c r="O226" t="s">
-        <v>518</v>
-      </c>
-      <c r="U226">
-        <v>1</v>
-      </c>
-      <c r="X226">
-        <v>1</v>
-      </c>
-      <c r="Z226">
-        <v>1</v>
+        <v>338</v>
       </c>
     </row>
     <row r="227" spans="1:30">
       <c r="A227">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B227">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="C227" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D227" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="E227" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="F227">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G227">
-        <v>8</v>
-      </c>
-      <c r="H227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K227">
         <v>1</v>
       </c>
-      <c r="P227">
-        <v>1</v>
-      </c>
-      <c r="W227">
+      <c r="Q227">
         <v>1</v>
       </c>
       <c r="Z227">
@@ -12684,238 +12664,241 @@
     </row>
     <row r="228" spans="1:30">
       <c r="A228">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B228">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="C228" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D228" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E228" t="s">
-        <v>335</v>
-      </c>
-      <c r="F228">
-        <v>48</v>
-      </c>
-      <c r="G228">
-        <v>3</v>
-      </c>
-      <c r="I228">
-        <v>1</v>
-      </c>
-      <c r="L228">
-        <v>1</v>
-      </c>
-      <c r="Q228">
-        <v>1</v>
-      </c>
-      <c r="U228">
-        <v>1</v>
-      </c>
-      <c r="AC228">
-        <v>1</v>
+        <v>342</v>
       </c>
     </row>
     <row r="229" spans="1:30">
       <c r="A229">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B229">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C229" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D229" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E229" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F229">
-        <v>43</v>
-      </c>
-      <c r="H229">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="G229">
+        <v>4</v>
       </c>
       <c r="K229">
         <v>1</v>
       </c>
-      <c r="P229">
-        <v>1</v>
-      </c>
-      <c r="W229">
-        <v>1</v>
-      </c>
-      <c r="AA229">
+      <c r="Q229">
         <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:30">
       <c r="A230">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B230">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C230" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D230" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E230" t="s">
-        <v>341</v>
-      </c>
-      <c r="F230">
-        <v>65</v>
-      </c>
-      <c r="G230">
-        <v>7</v>
-      </c>
-      <c r="H230">
-        <v>1</v>
+        <v>348</v>
       </c>
     </row>
     <row r="231" spans="1:30">
       <c r="A231">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B231">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="C231" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D231" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E231" t="s">
-        <v>344</v>
+        <v>350</v>
+      </c>
+      <c r="F231">
+        <v>31</v>
+      </c>
+      <c r="G231">
+        <v>4</v>
+      </c>
+      <c r="J231">
+        <v>1</v>
+      </c>
+      <c r="K231">
+        <v>1</v>
+      </c>
+      <c r="P231">
+        <v>1</v>
+      </c>
+      <c r="V231">
+        <v>1</v>
+      </c>
+      <c r="X231">
+        <v>1</v>
+      </c>
+      <c r="AC231">
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:30">
       <c r="A232">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B232">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="C232" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D232" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E232" t="s">
-        <v>346</v>
-      </c>
-      <c r="F232">
-        <v>65</v>
-      </c>
-      <c r="G232">
-        <v>2</v>
-      </c>
-      <c r="K232">
-        <v>1</v>
-      </c>
-      <c r="Q232">
-        <v>1</v>
-      </c>
-      <c r="Z232">
-        <v>1</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:30">
       <c r="A233">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B233">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="C233" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D233" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="E233" t="s">
-        <v>348</v>
+        <v>355</v>
+      </c>
+      <c r="F233">
+        <v>52</v>
+      </c>
+      <c r="G233">
+        <v>2</v>
+      </c>
+      <c r="H233">
+        <v>1</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="Q233">
+        <v>1</v>
+      </c>
+      <c r="V233">
+        <v>1</v>
+      </c>
+      <c r="X233">
+        <v>1</v>
+      </c>
+      <c r="AD233">
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:30">
       <c r="A234">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B234">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C234" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D234" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E234" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="F234">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G234">
-        <v>4</v>
-      </c>
-      <c r="K234">
-        <v>1</v>
-      </c>
-      <c r="Q234">
+        <v>5</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>1</v>
+      </c>
+      <c r="T234">
+        <v>1</v>
+      </c>
+      <c r="AD234">
         <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:30">
       <c r="A235">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B235">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="C235" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D235" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E235" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="236" spans="1:30">
       <c r="A236">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B236">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C236" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D236" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="E236" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F236">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G236">
-        <v>4</v>
-      </c>
-      <c r="J236">
+        <v>10</v>
+      </c>
+      <c r="H236">
         <v>1</v>
       </c>
       <c r="K236">
@@ -12924,193 +12907,42 @@
       <c r="P236">
         <v>1</v>
       </c>
-      <c r="V236">
-        <v>1</v>
-      </c>
-      <c r="X236">
-        <v>1</v>
-      </c>
-      <c r="AC236">
+      <c r="W236">
+        <v>1</v>
+      </c>
+      <c r="Z236">
         <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:30">
       <c r="A237">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B237">
-        <v>288</v>
+        <v>57</v>
       </c>
       <c r="C237" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D237" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E237" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="238" spans="1:30">
-      <c r="A238">
-        <v>237</v>
-      </c>
-      <c r="B238">
-        <v>243</v>
-      </c>
-      <c r="C238" t="s">
-        <v>360</v>
-      </c>
-      <c r="D238" t="s">
-        <v>357</v>
-      </c>
-      <c r="E238" t="s">
-        <v>361</v>
-      </c>
-      <c r="F238">
-        <v>52</v>
-      </c>
-      <c r="G238">
-        <v>2</v>
-      </c>
-      <c r="H238">
-        <v>1</v>
-      </c>
-      <c r="K238">
-        <v>1</v>
-      </c>
-      <c r="Q238">
-        <v>1</v>
-      </c>
-      <c r="V238">
-        <v>1</v>
-      </c>
-      <c r="X238">
-        <v>1</v>
-      </c>
-      <c r="AD238">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239" spans="1:30">
-      <c r="A239">
-        <v>238</v>
-      </c>
-      <c r="B239">
-        <v>244</v>
-      </c>
-      <c r="C239" t="s">
-        <v>363</v>
-      </c>
-      <c r="D239" t="s">
-        <v>362</v>
-      </c>
-      <c r="E239" t="s">
-        <v>364</v>
-      </c>
-      <c r="F239">
-        <v>69</v>
-      </c>
-      <c r="G239">
-        <v>5</v>
-      </c>
-      <c r="I239">
-        <v>1</v>
-      </c>
-      <c r="L239">
-        <v>1</v>
-      </c>
-      <c r="T239">
-        <v>1</v>
-      </c>
-      <c r="AD239">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:30">
-      <c r="A240">
-        <v>239</v>
-      </c>
-      <c r="B240">
-        <v>260</v>
-      </c>
-      <c r="C240" t="s">
-        <v>365</v>
-      </c>
-      <c r="D240" t="s">
-        <v>362</v>
-      </c>
-      <c r="E240" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="241" spans="1:30">
-      <c r="A241">
-        <v>240</v>
-      </c>
-      <c r="B241">
-        <v>242</v>
-      </c>
-      <c r="C241" t="s">
-        <v>368</v>
-      </c>
-      <c r="D241" t="s">
-        <v>367</v>
-      </c>
-      <c r="E241" t="s">
-        <v>369</v>
-      </c>
-      <c r="F241">
-        <v>56</v>
-      </c>
-      <c r="G241">
-        <v>10</v>
-      </c>
-      <c r="H241">
-        <v>1</v>
-      </c>
-      <c r="K241">
-        <v>1</v>
-      </c>
-      <c r="P241">
-        <v>1</v>
-      </c>
-      <c r="W241">
-        <v>1</v>
-      </c>
-      <c r="Z241">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:30">
-      <c r="A242">
-        <v>241</v>
-      </c>
-      <c r="B242">
-        <v>57</v>
-      </c>
-      <c r="C242" t="s">
-        <v>371</v>
-      </c>
-      <c r="D242" t="s">
-        <v>370</v>
-      </c>
-      <c r="E242" t="s">
-        <v>372</v>
-      </c>
-      <c r="F242">
+      <c r="F237">
         <v>61</v>
       </c>
-      <c r="G242">
+      <c r="G237">
         <v>4</v>
       </c>
-      <c r="I242">
-        <v>1</v>
-      </c>
-      <c r="T242">
-        <v>1</v>
-      </c>
-      <c r="AD242">
+      <c r="I237">
+        <v>1</v>
+      </c>
+      <c r="T237">
+        <v>1</v>
+      </c>
+      <c r="AD237">
         <v>1</v>
       </c>
     </row>

--- a/data/data_shichigawahama_w4.xlsx
+++ b/data/data_shichigawahama_w4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\r_analysis\shichigahama_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511C3FC6-5BDF-423D-B509-95FAD554DC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D30E70-ED6D-48CA-A5A6-F4F27D68ACE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5018,10 +5018,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>v35_farming_intention__maintain_status_quo_w4</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>v35_farming_intention_reduction_w4</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -5083,6 +5079,10 @@
   </si>
   <si>
     <t>wave4</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>v35_farming_intention_maintain_status_quo_w4</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -5483,10 +5483,10 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D1" t="s">
         <v>533</v>
-      </c>
-      <c r="D1" t="s">
-        <v>534</v>
       </c>
       <c r="E1" t="s">
         <v>368</v>
@@ -5528,46 +5528,46 @@
         <v>517</v>
       </c>
       <c r="R1" t="s">
+        <v>534</v>
+      </c>
+      <c r="S1" t="s">
         <v>518</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>519</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>520</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>521</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" t="s">
         <v>523</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>524</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>525</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>526</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>527</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>528</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>529</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>530</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="2" spans="1:31">
@@ -12317,7 +12317,7 @@
         <v>56</v>
       </c>
       <c r="C196" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D196">
         <v>1</v>
